--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -6539,7 +6539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6555,9 +6555,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -39528,7 +39525,7 @@
       <c r="A688" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B688" s="7">
+      <c r="B688" s="1">
         <v>16763</v>
       </c>
       <c r="C688" s="1" t="s">

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99035461-A766-4A71-8101-9CFDBDB2B538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEA63A1-7F82-4F9D-BE4C-D81B61E5FD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8331" uniqueCount="2169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8367" uniqueCount="2178">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -6541,6 +6541,33 @@
   </si>
   <si>
     <t>JK04L8007</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH959510</t>
+  </si>
+  <si>
+    <t>K12NP7889118</t>
+  </si>
+  <si>
+    <t>JK03R6843</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH974224</t>
+  </si>
+  <si>
+    <t>K12NP7898964</t>
+  </si>
+  <si>
+    <t>JK13L0242</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH969446</t>
+  </si>
+  <si>
+    <t>K12NP7895696</t>
+  </si>
+  <si>
+    <t>JK13L9721</t>
   </si>
 </sst>
 </file>
@@ -6556,15 +6583,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -6572,11 +6605,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6588,13 +6632,61 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="34">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -6658,6 +6750,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -6924,24 +7019,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O694" dataDxfId="29">
-  <autoFilter ref="A1:O694" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O697" dataDxfId="33">
+  <autoFilter ref="A1:O697" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" dataDxfId="0" totalsRowDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="4" totalsRowDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" dataDxfId="2" totalsRowDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" dataDxfId="5" totalsRowDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -39882,31 +39977,145 @@
       </c>
     </row>
     <row r="695" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A695" s="1"/>
-      <c r="B695" s="1"/>
-      <c r="C695" s="1"/>
-      <c r="D695" s="1"/>
-      <c r="E695" s="1"/>
-      <c r="F695" s="1"/>
-      <c r="G695" s="1"/>
-      <c r="H695" s="1"/>
-      <c r="I695" s="1"/>
-      <c r="J695" s="1"/>
-      <c r="K695" s="1"/>
-      <c r="L695" s="4"/>
-      <c r="M695" s="1"/>
-      <c r="N695" s="1"/>
-      <c r="O695" s="3"/>
+      <c r="A695" t="s">
+        <v>15</v>
+      </c>
+      <c r="B695">
+        <v>16763</v>
+      </c>
+      <c r="C695" t="s">
+        <v>16</v>
+      </c>
+      <c r="D695" t="s">
+        <v>2169</v>
+      </c>
+      <c r="E695" t="s">
+        <v>2170</v>
+      </c>
+      <c r="F695" t="s">
+        <v>19</v>
+      </c>
+      <c r="G695" t="s">
+        <v>20</v>
+      </c>
+      <c r="H695" t="s">
+        <v>40</v>
+      </c>
+      <c r="I695" t="s">
+        <v>40</v>
+      </c>
+      <c r="J695" t="s">
+        <v>29</v>
+      </c>
+      <c r="K695" t="s">
+        <v>23</v>
+      </c>
+      <c r="L695" s="4">
+        <v>46235</v>
+      </c>
+      <c r="M695" t="s">
+        <v>2171</v>
+      </c>
+      <c r="N695" s="5">
+        <v>46275</v>
+      </c>
+      <c r="O695" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="696" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L696" s="4"/>
-      <c r="M696" s="1"/>
-      <c r="N696" s="1"/>
+      <c r="A696" t="s">
+        <v>15</v>
+      </c>
+      <c r="B696">
+        <v>16763</v>
+      </c>
+      <c r="C696" t="s">
+        <v>16</v>
+      </c>
+      <c r="D696" s="6" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E696" s="6" t="s">
+        <v>2173</v>
+      </c>
+      <c r="F696" t="s">
+        <v>19</v>
+      </c>
+      <c r="G696" t="s">
+        <v>20</v>
+      </c>
+      <c r="H696" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I696" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J696" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K696" t="s">
+        <v>23</v>
+      </c>
+      <c r="L696" s="4">
+        <v>46235</v>
+      </c>
+      <c r="M696" s="6" t="s">
+        <v>2174</v>
+      </c>
+      <c r="N696" s="5">
+        <v>46275</v>
+      </c>
+      <c r="O696" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="697" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L697" s="4"/>
-      <c r="M697" s="1"/>
-      <c r="N697" s="1"/>
+      <c r="A697" t="s">
+        <v>15</v>
+      </c>
+      <c r="B697">
+        <v>16763</v>
+      </c>
+      <c r="C697" t="s">
+        <v>16</v>
+      </c>
+      <c r="D697" s="7" t="s">
+        <v>2175</v>
+      </c>
+      <c r="E697" s="7" t="s">
+        <v>2176</v>
+      </c>
+      <c r="F697" t="s">
+        <v>19</v>
+      </c>
+      <c r="G697" t="s">
+        <v>20</v>
+      </c>
+      <c r="H697" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I697" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J697" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K697" t="s">
+        <v>23</v>
+      </c>
+      <c r="L697" s="4">
+        <v>46235</v>
+      </c>
+      <c r="M697" s="7" t="s">
+        <v>2177</v>
+      </c>
+      <c r="N697" s="5">
+        <v>46275</v>
+      </c>
+      <c r="O697" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="698" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L698" s="4"/>
@@ -39922,6 +40131,26 @@
       <c r="N700" s="1"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D696:E697">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I696:J697">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M696:M697">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H696:H697">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEA63A1-7F82-4F9D-BE4C-D81B61E5FD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B93F59-3D3D-41B5-AFA7-3CCC1BE903AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8367" uniqueCount="2178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8379" uniqueCount="2181">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -6568,6 +6568,15 @@
   </si>
   <si>
     <t>JK13L9721</t>
+  </si>
+  <si>
+    <t>MBHHWB13STGD53479</t>
+  </si>
+  <si>
+    <t>K12NP4993043</t>
+  </si>
+  <si>
+    <t>JK13L0231</t>
   </si>
 </sst>
 </file>
@@ -6643,7 +6652,40 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -7019,24 +7061,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O697" dataDxfId="33">
-  <autoFilter ref="A1:O697" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O698" dataDxfId="36">
+  <autoFilter ref="A1:O698" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" dataDxfId="32" totalsRowDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" dataDxfId="8" totalsRowDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7339,7 +7381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O700"/>
+  <dimension ref="A1:O698"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -40118,35 +40160,84 @@
       </c>
     </row>
     <row r="698" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L698" s="4"/>
-      <c r="M698" s="1"/>
-      <c r="N698" s="1"/>
-    </row>
-    <row r="699" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M699" s="1"/>
-      <c r="N699" s="1"/>
-    </row>
-    <row r="700" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M700" s="1"/>
-      <c r="N700" s="1"/>
+      <c r="A698" t="s">
+        <v>15</v>
+      </c>
+      <c r="B698">
+        <v>16763</v>
+      </c>
+      <c r="C698" t="s">
+        <v>16</v>
+      </c>
+      <c r="D698" s="6" t="s">
+        <v>2178</v>
+      </c>
+      <c r="E698" s="6" t="s">
+        <v>2179</v>
+      </c>
+      <c r="F698" t="s">
+        <v>19</v>
+      </c>
+      <c r="G698" t="s">
+        <v>20</v>
+      </c>
+      <c r="H698" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I698" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J698" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K698" t="s">
+        <v>23</v>
+      </c>
+      <c r="L698" s="4">
+        <v>46204</v>
+      </c>
+      <c r="M698" s="6" t="s">
+        <v>2180</v>
+      </c>
+      <c r="N698" s="5">
+        <v>46276</v>
+      </c>
+      <c r="O698" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D696:E697">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H696:H697">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I696:J697">
+    <cfRule type="expression" dxfId="4" priority="6">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M696:M697">
+    <cfRule type="expression" dxfId="3" priority="5">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M698">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M696:M697">
+  <conditionalFormatting sqref="H698:J698">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H696:H697">
+  <conditionalFormatting sqref="D698:E698">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B93F59-3D3D-41B5-AFA7-3CCC1BE903AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C02DE60-F574-46EB-9C52-9DC3D42E5B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8379" uniqueCount="2181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8415" uniqueCount="2190">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -6577,6 +6577,33 @@
   </si>
   <si>
     <t>JK13L0231</t>
+  </si>
+  <si>
+    <t>MBHHWB13STGD38607</t>
+  </si>
+  <si>
+    <t>K12NP4979592</t>
+  </si>
+  <si>
+    <t>JK09E8551</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH962076</t>
+  </si>
+  <si>
+    <t>K12NP7890838</t>
+  </si>
+  <si>
+    <t>JK01BF6433</t>
+  </si>
+  <si>
+    <t>MBHHWB13STGD40164</t>
+  </si>
+  <si>
+    <t>K12NP4981013</t>
+  </si>
+  <si>
+    <t>JK05R0951</t>
   </si>
 </sst>
 </file>
@@ -6592,21 +6619,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -6614,22 +6635,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6641,40 +6651,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="35">
     <dxf>
       <font>
         <b/>
@@ -7061,24 +7042,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O698" dataDxfId="36">
-  <autoFilter ref="A1:O698" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O701" dataDxfId="34">
+  <autoFilter ref="A1:O701" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" dataDxfId="35" totalsRowDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" dataDxfId="32" totalsRowDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" dataDxfId="26" totalsRowDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" dataDxfId="6" totalsRowDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7381,7 +7362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O698"/>
+  <dimension ref="A1:O705"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -39447,7 +39428,7 @@
       <c r="M682" s="1" t="s">
         <v>2132</v>
       </c>
-      <c r="N682" s="1">
+      <c r="N682" s="3">
         <v>46269</v>
       </c>
       <c r="O682" s="1" t="s">
@@ -39494,7 +39475,7 @@
       <c r="M683" s="1" t="s">
         <v>2135</v>
       </c>
-      <c r="N683" s="1">
+      <c r="N683" s="3">
         <v>46269</v>
       </c>
       <c r="O683" s="1" t="s">
@@ -39541,7 +39522,7 @@
       <c r="M684" s="1" t="s">
         <v>2138</v>
       </c>
-      <c r="N684" s="1">
+      <c r="N684" s="3">
         <v>46269</v>
       </c>
       <c r="O684" s="1" t="s">
@@ -39588,7 +39569,7 @@
       <c r="M685" s="1" t="s">
         <v>2141</v>
       </c>
-      <c r="N685" s="1">
+      <c r="N685" s="3">
         <v>46269</v>
       </c>
       <c r="O685" s="1" t="s">
@@ -39635,7 +39616,7 @@
       <c r="M686" s="1" t="s">
         <v>2144</v>
       </c>
-      <c r="N686" s="1">
+      <c r="N686" s="3">
         <v>46269</v>
       </c>
       <c r="O686" s="3" t="s">
@@ -39682,7 +39663,7 @@
       <c r="M687" s="1" t="s">
         <v>2145</v>
       </c>
-      <c r="N687" s="1">
+      <c r="N687" s="3">
         <v>46270</v>
       </c>
       <c r="O687" s="3" t="s">
@@ -39729,7 +39710,7 @@
       <c r="M688" s="1" t="s">
         <v>2150</v>
       </c>
-      <c r="N688" s="1">
+      <c r="N688" s="3">
         <v>46270</v>
       </c>
       <c r="O688" s="3" t="s">
@@ -39776,10 +39757,10 @@
       <c r="M689" s="1" t="s">
         <v>2153</v>
       </c>
-      <c r="N689" s="1">
+      <c r="N689" s="3">
         <v>46273</v>
       </c>
-      <c r="O689" s="3" t="s">
+      <c r="O689" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -39823,10 +39804,10 @@
       <c r="M690" s="1" t="s">
         <v>2156</v>
       </c>
-      <c r="N690" s="1">
+      <c r="N690" s="3">
         <v>46273</v>
       </c>
-      <c r="O690" s="3" t="s">
+      <c r="O690" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -39870,10 +39851,10 @@
       <c r="M691" s="1" t="s">
         <v>2159</v>
       </c>
-      <c r="N691" s="1">
+      <c r="N691" s="3">
         <v>46274</v>
       </c>
-      <c r="O691" s="3" t="s">
+      <c r="O691" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -39917,10 +39898,10 @@
       <c r="M692" s="1" t="s">
         <v>2162</v>
       </c>
-      <c r="N692" s="1">
+      <c r="N692" s="3">
         <v>46274</v>
       </c>
-      <c r="O692" s="3" t="s">
+      <c r="O692" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -39964,10 +39945,10 @@
       <c r="M693" s="1" t="s">
         <v>2165</v>
       </c>
-      <c r="N693" s="1">
+      <c r="N693" s="3">
         <v>46274</v>
       </c>
-      <c r="O693" s="3" t="s">
+      <c r="O693" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -40011,237 +39992,358 @@
       <c r="M694" s="1" t="s">
         <v>2168</v>
       </c>
-      <c r="N694" s="1">
+      <c r="N694" s="3">
         <v>46274</v>
       </c>
-      <c r="O694" s="3" t="s">
+      <c r="O694" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="695" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A695" t="s">
-        <v>15</v>
-      </c>
-      <c r="B695">
-        <v>16763</v>
-      </c>
-      <c r="C695" t="s">
-        <v>16</v>
-      </c>
-      <c r="D695" t="s">
+      <c r="A695" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B695" s="1">
+        <v>16763</v>
+      </c>
+      <c r="C695" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D695" s="1" t="s">
         <v>2169</v>
       </c>
-      <c r="E695" t="s">
+      <c r="E695" s="1" t="s">
         <v>2170</v>
       </c>
-      <c r="F695" t="s">
-        <v>19</v>
-      </c>
-      <c r="G695" t="s">
-        <v>20</v>
-      </c>
-      <c r="H695" t="s">
+      <c r="F695" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G695" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H695" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I695" t="s">
+      <c r="I695" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J695" t="s">
+      <c r="J695" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K695" t="s">
+      <c r="K695" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L695" s="4">
         <v>46235</v>
       </c>
-      <c r="M695" t="s">
+      <c r="M695" s="1" t="s">
         <v>2171</v>
       </c>
-      <c r="N695" s="5">
+      <c r="N695" s="3">
         <v>46275</v>
       </c>
-      <c r="O695" t="s">
+      <c r="O695" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="696" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A696" t="s">
-        <v>15</v>
-      </c>
-      <c r="B696">
-        <v>16763</v>
-      </c>
-      <c r="C696" t="s">
-        <v>16</v>
-      </c>
-      <c r="D696" s="6" t="s">
+      <c r="A696" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B696" s="1">
+        <v>16763</v>
+      </c>
+      <c r="C696" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D696" s="1" t="s">
         <v>2172</v>
       </c>
-      <c r="E696" s="6" t="s">
+      <c r="E696" s="1" t="s">
         <v>2173</v>
       </c>
-      <c r="F696" t="s">
-        <v>19</v>
-      </c>
-      <c r="G696" t="s">
-        <v>20</v>
-      </c>
-      <c r="H696" s="6" t="s">
+      <c r="F696" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G696" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H696" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I696" s="6" t="s">
+      <c r="I696" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J696" s="6" t="s">
+      <c r="J696" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K696" t="s">
+      <c r="K696" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L696" s="4">
         <v>46235</v>
       </c>
-      <c r="M696" s="6" t="s">
+      <c r="M696" s="1" t="s">
         <v>2174</v>
       </c>
-      <c r="N696" s="5">
+      <c r="N696" s="3">
         <v>46275</v>
       </c>
-      <c r="O696" t="s">
+      <c r="O696" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="697" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A697" t="s">
-        <v>15</v>
-      </c>
-      <c r="B697">
-        <v>16763</v>
-      </c>
-      <c r="C697" t="s">
-        <v>16</v>
-      </c>
-      <c r="D697" s="7" t="s">
+      <c r="A697" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B697" s="1">
+        <v>16763</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D697" s="1" t="s">
         <v>2175</v>
       </c>
-      <c r="E697" s="7" t="s">
+      <c r="E697" s="1" t="s">
         <v>2176</v>
       </c>
-      <c r="F697" t="s">
-        <v>19</v>
-      </c>
-      <c r="G697" t="s">
-        <v>20</v>
-      </c>
-      <c r="H697" s="7" t="s">
+      <c r="F697" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G697" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H697" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I697" s="7" t="s">
+      <c r="I697" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J697" s="7" t="s">
+      <c r="J697" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K697" t="s">
+      <c r="K697" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L697" s="4">
         <v>46235</v>
       </c>
-      <c r="M697" s="7" t="s">
+      <c r="M697" s="1" t="s">
         <v>2177</v>
       </c>
-      <c r="N697" s="5">
+      <c r="N697" s="3">
         <v>46275</v>
       </c>
-      <c r="O697" t="s">
+      <c r="O697" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="698" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A698" t="s">
-        <v>15</v>
-      </c>
-      <c r="B698">
-        <v>16763</v>
-      </c>
-      <c r="C698" t="s">
-        <v>16</v>
-      </c>
-      <c r="D698" s="6" t="s">
+      <c r="A698" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B698" s="1">
+        <v>16763</v>
+      </c>
+      <c r="C698" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D698" s="1" t="s">
         <v>2178</v>
       </c>
-      <c r="E698" s="6" t="s">
+      <c r="E698" s="1" t="s">
         <v>2179</v>
       </c>
-      <c r="F698" t="s">
-        <v>19</v>
-      </c>
-      <c r="G698" t="s">
-        <v>20</v>
-      </c>
-      <c r="H698" s="6" t="s">
+      <c r="F698" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G698" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H698" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I698" s="6" t="s">
+      <c r="I698" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J698" s="6" t="s">
+      <c r="J698" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K698" t="s">
+      <c r="K698" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L698" s="4">
         <v>46204</v>
       </c>
-      <c r="M698" s="6" t="s">
+      <c r="M698" s="1" t="s">
         <v>2180</v>
       </c>
-      <c r="N698" s="5">
+      <c r="N698" s="3">
         <v>46276</v>
       </c>
-      <c r="O698" t="s">
-        <v>25</v>
-      </c>
+      <c r="O698" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="699" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A699" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B699" s="1">
+        <v>16763</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D699" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E699" s="1" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F699" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G699" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H699" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I699" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J699" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K699" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L699" s="4">
+        <v>46266</v>
+      </c>
+      <c r="M699" s="1" t="s">
+        <v>2183</v>
+      </c>
+      <c r="N699" s="3">
+        <v>46279</v>
+      </c>
+      <c r="O699" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="700" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A700" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B700" s="1">
+        <v>16763</v>
+      </c>
+      <c r="C700" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D700" s="1" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E700" s="1" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F700" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G700" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H700" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I700" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J700" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K700" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L700" s="4">
+        <v>46235</v>
+      </c>
+      <c r="M700" s="1" t="s">
+        <v>2186</v>
+      </c>
+      <c r="N700" s="3">
+        <v>46279</v>
+      </c>
+      <c r="O700" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="701" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A701" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B701" s="1">
+        <v>16763</v>
+      </c>
+      <c r="C701" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D701" s="1" t="s">
+        <v>2187</v>
+      </c>
+      <c r="E701" s="1" t="s">
+        <v>2188</v>
+      </c>
+      <c r="F701" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G701" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H701" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I701" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J701" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K701" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L701" s="4">
+        <v>46235</v>
+      </c>
+      <c r="M701" s="1" t="s">
+        <v>2189</v>
+      </c>
+      <c r="N701" s="3">
+        <v>46279</v>
+      </c>
+      <c r="O701" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="702" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L702" s="4"/>
+      <c r="M702" s="1"/>
+      <c r="O702" s="1"/>
+    </row>
+    <row r="703" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L703" s="4"/>
+      <c r="O703" s="1"/>
+    </row>
+    <row r="704" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O704" s="1"/>
+    </row>
+    <row r="705" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O705" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D696:E697">
-    <cfRule type="expression" dxfId="6" priority="7">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H696:H697">
-    <cfRule type="expression" dxfId="5" priority="4">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I696:J697">
-    <cfRule type="expression" dxfId="4" priority="6">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M696:M697">
-    <cfRule type="expression" dxfId="3" priority="5">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M698">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H698:J698">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D698:E698">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C02DE60-F574-46EB-9C52-9DC3D42E5B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B638AB6-26CA-4D9A-B283-81CB9FB55B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8415" uniqueCount="2190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8439" uniqueCount="2196">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -6604,6 +6604,24 @@
   </si>
   <si>
     <t>JK05R0951</t>
+  </si>
+  <si>
+    <t>MBHHWB13STGD53946</t>
+  </si>
+  <si>
+    <t>K12NP4993448</t>
+  </si>
+  <si>
+    <t>JK04L4331</t>
+  </si>
+  <si>
+    <t>MBHHWB13STGD35729</t>
+  </si>
+  <si>
+    <t>K12NP4976914</t>
+  </si>
+  <si>
+    <t>JK02DW9295</t>
   </si>
 </sst>
 </file>
@@ -6639,7 +6657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6651,66 +6669,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="30">
     <dxf>
       <font>
         <b val="0"/>
@@ -7042,24 +7006,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O701" dataDxfId="34">
-  <autoFilter ref="A1:O701" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O703" dataDxfId="29">
+  <autoFilter ref="A1:O703" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" dataDxfId="26" totalsRowDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -40329,13 +40293,98 @@
       </c>
     </row>
     <row r="702" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L702" s="4"/>
-      <c r="M702" s="1"/>
-      <c r="O702" s="1"/>
+      <c r="A702" t="s">
+        <v>15</v>
+      </c>
+      <c r="B702">
+        <v>16763</v>
+      </c>
+      <c r="C702" t="s">
+        <v>16</v>
+      </c>
+      <c r="D702" t="s">
+        <v>2190</v>
+      </c>
+      <c r="E702" t="s">
+        <v>2191</v>
+      </c>
+      <c r="F702" t="s">
+        <v>19</v>
+      </c>
+      <c r="G702" t="s">
+        <v>20</v>
+      </c>
+      <c r="H702" t="s">
+        <v>28</v>
+      </c>
+      <c r="I702" t="s">
+        <v>28</v>
+      </c>
+      <c r="J702" t="s">
+        <v>115</v>
+      </c>
+      <c r="K702" t="s">
+        <v>23</v>
+      </c>
+      <c r="L702" s="4">
+        <v>46235</v>
+      </c>
+      <c r="M702" t="s">
+        <v>2192</v>
+      </c>
+      <c r="N702" s="5">
+        <v>46280</v>
+      </c>
+      <c r="O702" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="703" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L703" s="4"/>
-      <c r="O703" s="1"/>
+      <c r="A703" t="s">
+        <v>15</v>
+      </c>
+      <c r="B703">
+        <v>16763</v>
+      </c>
+      <c r="C703" t="s">
+        <v>16</v>
+      </c>
+      <c r="D703" t="s">
+        <v>2193</v>
+      </c>
+      <c r="E703" t="s">
+        <v>2194</v>
+      </c>
+      <c r="F703" t="s">
+        <v>19</v>
+      </c>
+      <c r="G703" t="s">
+        <v>20</v>
+      </c>
+      <c r="H703" t="s">
+        <v>162</v>
+      </c>
+      <c r="I703" t="s">
+        <v>162</v>
+      </c>
+      <c r="J703" t="s">
+        <v>54</v>
+      </c>
+      <c r="K703" t="s">
+        <v>23</v>
+      </c>
+      <c r="L703" s="4">
+        <v>46235</v>
+      </c>
+      <c r="M703" t="s">
+        <v>2195</v>
+      </c>
+      <c r="N703" s="5">
+        <v>46280</v>
+      </c>
+      <c r="O703" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="704" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O704" s="1"/>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA77E1AC-6C1E-4C2D-A40D-2684858FFC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8660D28F-90F9-45AF-BEA4-F7BB6BE71AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8511" uniqueCount="2214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8595" uniqueCount="2237">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -6676,6 +6676,75 @@
   </si>
   <si>
     <t>JK13L0445</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH953701</t>
+  </si>
+  <si>
+    <t>K12NP7884935</t>
+  </si>
+  <si>
+    <t>JK05R1128</t>
+  </si>
+  <si>
+    <t>MBJTYKL1STB362874</t>
+  </si>
+  <si>
+    <t>K15CN7906892</t>
+  </si>
+  <si>
+    <t>JK01BF6956</t>
+  </si>
+  <si>
+    <t>MBHHWBC3STHD73572</t>
+  </si>
+  <si>
+    <t>Z12EP4003646</t>
+  </si>
+  <si>
+    <t>BALENO ALPHA (O)</t>
+  </si>
+  <si>
+    <t>PRME ENIGMATIC TEAL</t>
+  </si>
+  <si>
+    <t>JK01BF7799</t>
+  </si>
+  <si>
+    <t>MBHHWB13STHD58868</t>
+  </si>
+  <si>
+    <t>K12NP4997790</t>
+  </si>
+  <si>
+    <t>JK01BF6902</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ984858</t>
+  </si>
+  <si>
+    <t>K12NP7906890</t>
+  </si>
+  <si>
+    <t>JK13L0595</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH969951</t>
+  </si>
+  <si>
+    <t>K12NP7895975</t>
+  </si>
+  <si>
+    <t>JK13L0594</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH977043</t>
+  </si>
+  <si>
+    <t>K12NP7901025</t>
+  </si>
+  <si>
+    <t>JK04L4527</t>
   </si>
 </sst>
 </file>
@@ -6711,11 +6780,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7001,8 +7072,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O709">
-  <autoFilter ref="A1:O709" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O716">
+  <autoFilter ref="A1:O716" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="13"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -7321,7 +7392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O709"/>
+  <dimension ref="A1:O716"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -40663,6 +40734,335 @@
         <v>25</v>
       </c>
     </row>
+    <row r="710" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A710" t="s">
+        <v>15</v>
+      </c>
+      <c r="B710">
+        <v>16763</v>
+      </c>
+      <c r="C710" t="s">
+        <v>16</v>
+      </c>
+      <c r="D710" t="s">
+        <v>2214</v>
+      </c>
+      <c r="E710" t="s">
+        <v>2215</v>
+      </c>
+      <c r="F710" t="s">
+        <v>19</v>
+      </c>
+      <c r="G710" t="s">
+        <v>20</v>
+      </c>
+      <c r="H710" t="s">
+        <v>40</v>
+      </c>
+      <c r="I710" t="s">
+        <v>40</v>
+      </c>
+      <c r="J710" t="s">
+        <v>115</v>
+      </c>
+      <c r="K710" t="s">
+        <v>23</v>
+      </c>
+      <c r="L710" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M710" t="s">
+        <v>2216</v>
+      </c>
+      <c r="N710" s="3">
+        <v>46282</v>
+      </c>
+      <c r="O710" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="711" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A711" t="s">
+        <v>15</v>
+      </c>
+      <c r="B711">
+        <v>16763</v>
+      </c>
+      <c r="C711" t="s">
+        <v>16</v>
+      </c>
+      <c r="D711" t="s">
+        <v>2217</v>
+      </c>
+      <c r="E711" t="s">
+        <v>2218</v>
+      </c>
+      <c r="F711" t="s">
+        <v>19</v>
+      </c>
+      <c r="G711" t="s">
+        <v>20</v>
+      </c>
+      <c r="H711" t="s">
+        <v>753</v>
+      </c>
+      <c r="I711" t="s">
+        <v>753</v>
+      </c>
+      <c r="J711" t="s">
+        <v>29</v>
+      </c>
+      <c r="K711" t="s">
+        <v>46</v>
+      </c>
+      <c r="L711" s="2">
+        <v>46054</v>
+      </c>
+      <c r="M711" t="s">
+        <v>2219</v>
+      </c>
+      <c r="N711" s="3">
+        <v>46283</v>
+      </c>
+      <c r="O711" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="712" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A712" t="s">
+        <v>15</v>
+      </c>
+      <c r="B712">
+        <v>16763</v>
+      </c>
+      <c r="C712" t="s">
+        <v>16</v>
+      </c>
+      <c r="D712" t="s">
+        <v>2220</v>
+      </c>
+      <c r="E712" t="s">
+        <v>2221</v>
+      </c>
+      <c r="F712" t="s">
+        <v>19</v>
+      </c>
+      <c r="G712" t="s">
+        <v>20</v>
+      </c>
+      <c r="H712" t="s">
+        <v>2222</v>
+      </c>
+      <c r="I712" t="s">
+        <v>2222</v>
+      </c>
+      <c r="J712" t="s">
+        <v>2223</v>
+      </c>
+      <c r="K712" t="s">
+        <v>23</v>
+      </c>
+      <c r="L712" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M712" t="s">
+        <v>2224</v>
+      </c>
+      <c r="N712" s="3">
+        <v>46283</v>
+      </c>
+      <c r="O712" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="713" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A713" t="s">
+        <v>15</v>
+      </c>
+      <c r="B713">
+        <v>16763</v>
+      </c>
+      <c r="C713" t="s">
+        <v>16</v>
+      </c>
+      <c r="D713" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E713" t="s">
+        <v>2226</v>
+      </c>
+      <c r="F713" t="s">
+        <v>19</v>
+      </c>
+      <c r="G713" t="s">
+        <v>20</v>
+      </c>
+      <c r="H713" t="s">
+        <v>162</v>
+      </c>
+      <c r="I713" t="s">
+        <v>162</v>
+      </c>
+      <c r="J713" t="s">
+        <v>29</v>
+      </c>
+      <c r="K713" t="s">
+        <v>23</v>
+      </c>
+      <c r="L713" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M713" t="s">
+        <v>2227</v>
+      </c>
+      <c r="N713" s="3">
+        <v>46283</v>
+      </c>
+      <c r="O713" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="714" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A714" t="s">
+        <v>15</v>
+      </c>
+      <c r="B714">
+        <v>16763</v>
+      </c>
+      <c r="C714" t="s">
+        <v>16</v>
+      </c>
+      <c r="D714" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E714" t="s">
+        <v>2229</v>
+      </c>
+      <c r="F714" t="s">
+        <v>19</v>
+      </c>
+      <c r="G714" t="s">
+        <v>20</v>
+      </c>
+      <c r="H714" t="s">
+        <v>53</v>
+      </c>
+      <c r="I714" t="s">
+        <v>53</v>
+      </c>
+      <c r="J714" t="s">
+        <v>54</v>
+      </c>
+      <c r="K714" t="s">
+        <v>23</v>
+      </c>
+      <c r="L714" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M714" t="s">
+        <v>2230</v>
+      </c>
+      <c r="N714" s="3">
+        <v>46283</v>
+      </c>
+      <c r="O714" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="715" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A715" t="s">
+        <v>15</v>
+      </c>
+      <c r="B715">
+        <v>16763</v>
+      </c>
+      <c r="C715" t="s">
+        <v>16</v>
+      </c>
+      <c r="D715" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E715" t="s">
+        <v>2232</v>
+      </c>
+      <c r="F715" t="s">
+        <v>19</v>
+      </c>
+      <c r="G715" t="s">
+        <v>20</v>
+      </c>
+      <c r="H715" t="s">
+        <v>40</v>
+      </c>
+      <c r="I715" t="s">
+        <v>40</v>
+      </c>
+      <c r="J715" t="s">
+        <v>29</v>
+      </c>
+      <c r="K715" t="s">
+        <v>23</v>
+      </c>
+      <c r="L715" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M715" t="s">
+        <v>2233</v>
+      </c>
+      <c r="N715" s="3">
+        <v>46283</v>
+      </c>
+      <c r="O715" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="716" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A716" t="s">
+        <v>15</v>
+      </c>
+      <c r="B716">
+        <v>16763</v>
+      </c>
+      <c r="C716" t="s">
+        <v>16</v>
+      </c>
+      <c r="D716" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E716" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F716" t="s">
+        <v>19</v>
+      </c>
+      <c r="G716" t="s">
+        <v>20</v>
+      </c>
+      <c r="H716" t="s">
+        <v>53</v>
+      </c>
+      <c r="I716" t="s">
+        <v>53</v>
+      </c>
+      <c r="J716" t="s">
+        <v>29</v>
+      </c>
+      <c r="K716" t="s">
+        <v>23</v>
+      </c>
+      <c r="L716" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M716" t="s">
+        <v>2236</v>
+      </c>
+      <c r="N716" s="3">
+        <v>46283</v>
+      </c>
+      <c r="O716" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8660D28F-90F9-45AF-BEA4-F7BB6BE71AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF998FD5-A1C6-4998-B3E0-A0EE8C2EF508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8595" uniqueCount="2237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8667" uniqueCount="2255">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -6745,6 +6745,60 @@
   </si>
   <si>
     <t>JK04L4527</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH974634</t>
+  </si>
+  <si>
+    <t>K12NP7899270</t>
+  </si>
+  <si>
+    <t>JK13L0554</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH977396</t>
+  </si>
+  <si>
+    <t>K12NP7901308</t>
+  </si>
+  <si>
+    <t>JK02DX0206</t>
+  </si>
+  <si>
+    <t>MBHHWB13STGD34544</t>
+  </si>
+  <si>
+    <t>K12NP4975839</t>
+  </si>
+  <si>
+    <t>JK05R1223</t>
+  </si>
+  <si>
+    <t>MBHHWB13STHD67182</t>
+  </si>
+  <si>
+    <t>K12NP5005173</t>
+  </si>
+  <si>
+    <t>JK01BF7196</t>
+  </si>
+  <si>
+    <t>MBHKWD13STG939952</t>
+  </si>
+  <si>
+    <t>K12NP7875351</t>
+  </si>
+  <si>
+    <t>JK04L4596</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH965952</t>
+  </si>
+  <si>
+    <t>K12NP7893391</t>
+  </si>
+  <si>
+    <t>JK13L0508</t>
   </si>
 </sst>
 </file>
@@ -7072,8 +7126,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O716">
-  <autoFilter ref="A1:O716" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O722">
+  <autoFilter ref="A1:O722" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="13"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -7392,7 +7446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O716"/>
+  <dimension ref="A1:O722"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -41063,6 +41117,288 @@
         <v>25</v>
       </c>
     </row>
+    <row r="717" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A717" t="s">
+        <v>15</v>
+      </c>
+      <c r="B717">
+        <v>16763</v>
+      </c>
+      <c r="C717" t="s">
+        <v>16</v>
+      </c>
+      <c r="D717" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E717" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F717" t="s">
+        <v>19</v>
+      </c>
+      <c r="G717" t="s">
+        <v>20</v>
+      </c>
+      <c r="H717" t="s">
+        <v>53</v>
+      </c>
+      <c r="I717" t="s">
+        <v>53</v>
+      </c>
+      <c r="J717" t="s">
+        <v>54</v>
+      </c>
+      <c r="K717" t="s">
+        <v>23</v>
+      </c>
+      <c r="L717" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M717" t="s">
+        <v>2239</v>
+      </c>
+      <c r="N717" s="3">
+        <v>46284</v>
+      </c>
+      <c r="O717" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="718" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A718" t="s">
+        <v>15</v>
+      </c>
+      <c r="B718">
+        <v>16763</v>
+      </c>
+      <c r="C718" t="s">
+        <v>16</v>
+      </c>
+      <c r="D718" t="s">
+        <v>2240</v>
+      </c>
+      <c r="E718" t="s">
+        <v>2241</v>
+      </c>
+      <c r="F718" t="s">
+        <v>19</v>
+      </c>
+      <c r="G718" t="s">
+        <v>20</v>
+      </c>
+      <c r="H718" t="s">
+        <v>53</v>
+      </c>
+      <c r="I718" t="s">
+        <v>53</v>
+      </c>
+      <c r="J718" t="s">
+        <v>115</v>
+      </c>
+      <c r="K718" t="s">
+        <v>23</v>
+      </c>
+      <c r="L718" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M718" t="s">
+        <v>2242</v>
+      </c>
+      <c r="N718" s="3">
+        <v>46284</v>
+      </c>
+      <c r="O718" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="719" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A719" t="s">
+        <v>15</v>
+      </c>
+      <c r="B719">
+        <v>16763</v>
+      </c>
+      <c r="C719" t="s">
+        <v>16</v>
+      </c>
+      <c r="D719" t="s">
+        <v>2243</v>
+      </c>
+      <c r="E719" t="s">
+        <v>2244</v>
+      </c>
+      <c r="F719" t="s">
+        <v>19</v>
+      </c>
+      <c r="G719" t="s">
+        <v>20</v>
+      </c>
+      <c r="H719" t="s">
+        <v>162</v>
+      </c>
+      <c r="I719" t="s">
+        <v>162</v>
+      </c>
+      <c r="J719" t="s">
+        <v>54</v>
+      </c>
+      <c r="K719" t="s">
+        <v>23</v>
+      </c>
+      <c r="L719" s="2">
+        <v>46204</v>
+      </c>
+      <c r="M719" t="s">
+        <v>2245</v>
+      </c>
+      <c r="N719" s="3">
+        <v>46284</v>
+      </c>
+      <c r="O719" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="720" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A720" t="s">
+        <v>15</v>
+      </c>
+      <c r="B720">
+        <v>16763</v>
+      </c>
+      <c r="C720" t="s">
+        <v>16</v>
+      </c>
+      <c r="D720" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E720" t="s">
+        <v>2247</v>
+      </c>
+      <c r="F720" t="s">
+        <v>19</v>
+      </c>
+      <c r="G720" t="s">
+        <v>20</v>
+      </c>
+      <c r="H720" t="s">
+        <v>28</v>
+      </c>
+      <c r="I720" t="s">
+        <v>28</v>
+      </c>
+      <c r="J720" t="s">
+        <v>1784</v>
+      </c>
+      <c r="K720" t="s">
+        <v>23</v>
+      </c>
+      <c r="L720" s="2">
+        <v>46204</v>
+      </c>
+      <c r="M720" t="s">
+        <v>2248</v>
+      </c>
+      <c r="N720" s="3">
+        <v>46284</v>
+      </c>
+      <c r="O720" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="721" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A721" t="s">
+        <v>15</v>
+      </c>
+      <c r="B721">
+        <v>16763</v>
+      </c>
+      <c r="C721" t="s">
+        <v>16</v>
+      </c>
+      <c r="D721" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E721" t="s">
+        <v>2250</v>
+      </c>
+      <c r="F721" t="s">
+        <v>19</v>
+      </c>
+      <c r="G721" t="s">
+        <v>20</v>
+      </c>
+      <c r="H721" t="s">
+        <v>53</v>
+      </c>
+      <c r="I721" t="s">
+        <v>53</v>
+      </c>
+      <c r="J721" t="s">
+        <v>1784</v>
+      </c>
+      <c r="K721" t="s">
+        <v>23</v>
+      </c>
+      <c r="L721" s="2">
+        <v>46204</v>
+      </c>
+      <c r="M721" t="s">
+        <v>2251</v>
+      </c>
+      <c r="N721" s="3">
+        <v>46284</v>
+      </c>
+      <c r="O721" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="722" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A722" t="s">
+        <v>15</v>
+      </c>
+      <c r="B722">
+        <v>16763</v>
+      </c>
+      <c r="C722" t="s">
+        <v>16</v>
+      </c>
+      <c r="D722" t="s">
+        <v>2252</v>
+      </c>
+      <c r="E722" t="s">
+        <v>2253</v>
+      </c>
+      <c r="F722" t="s">
+        <v>19</v>
+      </c>
+      <c r="G722" t="s">
+        <v>20</v>
+      </c>
+      <c r="H722" t="s">
+        <v>40</v>
+      </c>
+      <c r="I722" t="s">
+        <v>40</v>
+      </c>
+      <c r="J722" t="s">
+        <v>115</v>
+      </c>
+      <c r="K722" t="s">
+        <v>23</v>
+      </c>
+      <c r="L722" s="2">
+        <v>46204</v>
+      </c>
+      <c r="M722" t="s">
+        <v>2254</v>
+      </c>
+      <c r="N722" s="3">
+        <v>46284</v>
+      </c>
+      <c r="O722" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F742EFB7-8ED0-4F31-99F5-73E9AC1D8B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46B3F5D-D20A-4189-85AF-DA2CF804E54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8691" uniqueCount="2261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8751" uniqueCount="2276">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -6817,6 +6817,51 @@
   </si>
   <si>
     <t>JK05R1237</t>
+  </si>
+  <si>
+    <t>MBHHWB13STED00862</t>
+  </si>
+  <si>
+    <t>K12NP4946235</t>
+  </si>
+  <si>
+    <t>JK01BF8587</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ988226</t>
+  </si>
+  <si>
+    <t>K12NP7909395</t>
+  </si>
+  <si>
+    <t>JK13L0686</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ987766</t>
+  </si>
+  <si>
+    <t>K12NP7909053</t>
+  </si>
+  <si>
+    <t>JK03R7439</t>
+  </si>
+  <si>
+    <t>MBHHWBC3STJD86814</t>
+  </si>
+  <si>
+    <t>Z12EP4015438</t>
+  </si>
+  <si>
+    <t>JK01BF7404</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ989775</t>
+  </si>
+  <si>
+    <t>K12NP7910520</t>
+  </si>
+  <si>
+    <t>JK13L0625</t>
   </si>
 </sst>
 </file>
@@ -6865,10 +6910,45 @@
   </cellStyles>
   <dxfs count="16">
     <dxf>
-      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
     </dxf>
     <dxf>
       <font>
@@ -6909,42 +6989,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -7150,8 +7195,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O724">
-  <autoFilter ref="A1:O724" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O729">
+  <autoFilter ref="A1:O729" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="15"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -7164,10 +7209,10 @@
     <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" totalsRowDxfId="8"/>
     <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" totalsRowDxfId="7"/>
     <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" totalsRowDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="1" totalsRowDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="0" totalsRowDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="2" totalsRowDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7470,7 +7515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O724"/>
+  <dimension ref="A1:O729"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -41517,6 +41562,241 @@
         <v>25</v>
       </c>
     </row>
+    <row r="725" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A725" t="s">
+        <v>15</v>
+      </c>
+      <c r="B725">
+        <v>16763</v>
+      </c>
+      <c r="C725" t="s">
+        <v>16</v>
+      </c>
+      <c r="D725" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E725" t="s">
+        <v>2262</v>
+      </c>
+      <c r="F725" t="s">
+        <v>19</v>
+      </c>
+      <c r="G725" t="s">
+        <v>20</v>
+      </c>
+      <c r="H725" t="s">
+        <v>519</v>
+      </c>
+      <c r="I725" t="s">
+        <v>519</v>
+      </c>
+      <c r="J725" t="s">
+        <v>74</v>
+      </c>
+      <c r="K725" t="s">
+        <v>23</v>
+      </c>
+      <c r="L725" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M725" t="s">
+        <v>2263</v>
+      </c>
+      <c r="N725" s="3">
+        <v>46287</v>
+      </c>
+      <c r="O725" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="726" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A726" t="s">
+        <v>15</v>
+      </c>
+      <c r="B726">
+        <v>16763</v>
+      </c>
+      <c r="C726" t="s">
+        <v>16</v>
+      </c>
+      <c r="D726" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E726" t="s">
+        <v>2265</v>
+      </c>
+      <c r="F726" t="s">
+        <v>19</v>
+      </c>
+      <c r="G726" t="s">
+        <v>20</v>
+      </c>
+      <c r="H726" t="s">
+        <v>53</v>
+      </c>
+      <c r="I726" t="s">
+        <v>53</v>
+      </c>
+      <c r="J726" t="s">
+        <v>54</v>
+      </c>
+      <c r="K726" t="s">
+        <v>23</v>
+      </c>
+      <c r="L726" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M726" t="s">
+        <v>2266</v>
+      </c>
+      <c r="N726" s="3">
+        <v>46287</v>
+      </c>
+      <c r="O726" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="727" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A727" t="s">
+        <v>15</v>
+      </c>
+      <c r="B727">
+        <v>16763</v>
+      </c>
+      <c r="C727" t="s">
+        <v>16</v>
+      </c>
+      <c r="D727" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E727" t="s">
+        <v>2268</v>
+      </c>
+      <c r="F727" t="s">
+        <v>19</v>
+      </c>
+      <c r="G727" t="s">
+        <v>20</v>
+      </c>
+      <c r="H727" t="s">
+        <v>40</v>
+      </c>
+      <c r="I727" t="s">
+        <v>40</v>
+      </c>
+      <c r="J727" t="s">
+        <v>115</v>
+      </c>
+      <c r="K727" t="s">
+        <v>23</v>
+      </c>
+      <c r="L727" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M727" t="s">
+        <v>2269</v>
+      </c>
+      <c r="N727" s="3">
+        <v>46287</v>
+      </c>
+      <c r="O727" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="728" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A728" t="s">
+        <v>15</v>
+      </c>
+      <c r="B728">
+        <v>16763</v>
+      </c>
+      <c r="C728" t="s">
+        <v>16</v>
+      </c>
+      <c r="D728" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E728" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F728" t="s">
+        <v>19</v>
+      </c>
+      <c r="G728" t="s">
+        <v>20</v>
+      </c>
+      <c r="H728" t="s">
+        <v>28</v>
+      </c>
+      <c r="I728" t="s">
+        <v>28</v>
+      </c>
+      <c r="J728" t="s">
+        <v>29</v>
+      </c>
+      <c r="K728" t="s">
+        <v>23</v>
+      </c>
+      <c r="L728" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M728" t="s">
+        <v>2272</v>
+      </c>
+      <c r="N728" s="3">
+        <v>46287</v>
+      </c>
+      <c r="O728" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="729" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A729" t="s">
+        <v>15</v>
+      </c>
+      <c r="B729">
+        <v>16763</v>
+      </c>
+      <c r="C729" t="s">
+        <v>16</v>
+      </c>
+      <c r="D729" t="s">
+        <v>2273</v>
+      </c>
+      <c r="E729" t="s">
+        <v>2274</v>
+      </c>
+      <c r="F729" t="s">
+        <v>19</v>
+      </c>
+      <c r="G729" t="s">
+        <v>20</v>
+      </c>
+      <c r="H729" t="s">
+        <v>279</v>
+      </c>
+      <c r="I729" t="s">
+        <v>279</v>
+      </c>
+      <c r="J729" t="s">
+        <v>54</v>
+      </c>
+      <c r="K729" t="s">
+        <v>23</v>
+      </c>
+      <c r="L729" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M729" t="s">
+        <v>2275</v>
+      </c>
+      <c r="N729" s="3">
+        <v>46287</v>
+      </c>
+      <c r="O729" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46B3F5D-D20A-4189-85AF-DA2CF804E54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71D7D07-F827-40AE-964C-10C1F7320455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8751" uniqueCount="2276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8799" uniqueCount="2288">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -6862,6 +6862,42 @@
   </si>
   <si>
     <t>JK13L0625</t>
+  </si>
+  <si>
+    <t>JK13L0796</t>
+  </si>
+  <si>
+    <t>K15CN8042321</t>
+  </si>
+  <si>
+    <t>MBJTYKL1STH389793</t>
+  </si>
+  <si>
+    <t>MBHKWD13STG946454</t>
+  </si>
+  <si>
+    <t>K12NP7879876</t>
+  </si>
+  <si>
+    <t>JK13L0738</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ990640</t>
+  </si>
+  <si>
+    <t>K12NP7911204</t>
+  </si>
+  <si>
+    <t>JK13L0772</t>
+  </si>
+  <si>
+    <t>MBHHWB13STFD12228</t>
+  </si>
+  <si>
+    <t>K12NP4956719</t>
+  </si>
+  <si>
+    <t>JK21M3441</t>
   </si>
 </sst>
 </file>
@@ -7195,8 +7231,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O729">
-  <autoFilter ref="A1:O729" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O733">
+  <autoFilter ref="A1:O733" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="15"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -7515,7 +7551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O729"/>
+  <dimension ref="A1:O733"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -41797,6 +41833,194 @@
         <v>25</v>
       </c>
     </row>
+    <row r="730" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A730" t="s">
+        <v>15</v>
+      </c>
+      <c r="B730">
+        <v>16763</v>
+      </c>
+      <c r="C730" t="s">
+        <v>16</v>
+      </c>
+      <c r="D730" t="s">
+        <v>2278</v>
+      </c>
+      <c r="E730" t="s">
+        <v>2277</v>
+      </c>
+      <c r="F730" t="s">
+        <v>19</v>
+      </c>
+      <c r="G730" t="s">
+        <v>20</v>
+      </c>
+      <c r="H730" t="s">
+        <v>300</v>
+      </c>
+      <c r="I730" t="s">
+        <v>300</v>
+      </c>
+      <c r="J730" t="s">
+        <v>29</v>
+      </c>
+      <c r="K730" t="s">
+        <v>46</v>
+      </c>
+      <c r="L730" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M730" t="s">
+        <v>2276</v>
+      </c>
+      <c r="N730" s="3">
+        <v>46288</v>
+      </c>
+      <c r="O730" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="731" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A731" t="s">
+        <v>15</v>
+      </c>
+      <c r="B731">
+        <v>16763</v>
+      </c>
+      <c r="C731" t="s">
+        <v>16</v>
+      </c>
+      <c r="D731" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E731" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F731" t="s">
+        <v>19</v>
+      </c>
+      <c r="G731" t="s">
+        <v>20</v>
+      </c>
+      <c r="H731" t="s">
+        <v>40</v>
+      </c>
+      <c r="I731" t="s">
+        <v>40</v>
+      </c>
+      <c r="J731" t="s">
+        <v>115</v>
+      </c>
+      <c r="K731" t="s">
+        <v>23</v>
+      </c>
+      <c r="L731" s="2">
+        <v>46204</v>
+      </c>
+      <c r="M731" t="s">
+        <v>2281</v>
+      </c>
+      <c r="N731" s="3">
+        <v>46289</v>
+      </c>
+      <c r="O731" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="732" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A732" t="s">
+        <v>15</v>
+      </c>
+      <c r="B732">
+        <v>16763</v>
+      </c>
+      <c r="C732" t="s">
+        <v>16</v>
+      </c>
+      <c r="D732" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E732" t="s">
+        <v>2283</v>
+      </c>
+      <c r="F732" t="s">
+        <v>19</v>
+      </c>
+      <c r="G732" t="s">
+        <v>20</v>
+      </c>
+      <c r="H732" t="s">
+        <v>40</v>
+      </c>
+      <c r="I732" t="s">
+        <v>40</v>
+      </c>
+      <c r="J732" t="s">
+        <v>115</v>
+      </c>
+      <c r="K732" t="s">
+        <v>23</v>
+      </c>
+      <c r="L732" s="2">
+        <v>46204</v>
+      </c>
+      <c r="M732" t="s">
+        <v>2284</v>
+      </c>
+      <c r="N732" s="3">
+        <v>46289</v>
+      </c>
+      <c r="O732" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="733" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A733" t="s">
+        <v>15</v>
+      </c>
+      <c r="B733">
+        <v>16763</v>
+      </c>
+      <c r="C733" t="s">
+        <v>16</v>
+      </c>
+      <c r="D733" t="s">
+        <v>2285</v>
+      </c>
+      <c r="E733" t="s">
+        <v>2286</v>
+      </c>
+      <c r="F733" t="s">
+        <v>19</v>
+      </c>
+      <c r="G733" t="s">
+        <v>20</v>
+      </c>
+      <c r="H733" t="s">
+        <v>519</v>
+      </c>
+      <c r="I733" t="s">
+        <v>519</v>
+      </c>
+      <c r="J733" t="s">
+        <v>54</v>
+      </c>
+      <c r="K733" t="s">
+        <v>23</v>
+      </c>
+      <c r="L733" s="2">
+        <v>46204</v>
+      </c>
+      <c r="M733" t="s">
+        <v>2287</v>
+      </c>
+      <c r="N733" s="3">
+        <v>46289</v>
+      </c>
+      <c r="O733" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71D7D07-F827-40AE-964C-10C1F7320455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0620EAC8-3779-4EF1-979F-03D7D70AC815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8799" uniqueCount="2288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8823" uniqueCount="2294">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -6898,6 +6898,24 @@
   </si>
   <si>
     <t>JK21M3441</t>
+  </si>
+  <si>
+    <t>MBHHWBC3STJD81036</t>
+  </si>
+  <si>
+    <t>Z12EP4010000</t>
+  </si>
+  <si>
+    <t>26BH4409R</t>
+  </si>
+  <si>
+    <t>MBHHWB13STHD66305</t>
+  </si>
+  <si>
+    <t>K12NP5004301</t>
+  </si>
+  <si>
+    <t>JK09E9119</t>
   </si>
 </sst>
 </file>
@@ -6921,7 +6939,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -6929,22 +6947,80 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -7231,24 +7307,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O733">
-  <autoFilter ref="A1:O733" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O735">
+  <autoFilter ref="A1:O735" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
-    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" totalsRowDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" totalsRowDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" totalsRowDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" totalsRowDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" totalsRowDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" totalsRowDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" totalsRowDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" totalsRowDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" totalsRowDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="2" totalsRowDxfId="1"/>
-    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" totalsRowDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" totalsRowDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" totalsRowDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" totalsRowDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" totalsRowDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" totalsRowDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" totalsRowDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" totalsRowDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" totalsRowDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7551,7 +7627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O733"/>
+  <dimension ref="A1:O735"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -42021,7 +42097,121 @@
         <v>25</v>
       </c>
     </row>
+    <row r="734" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A734" t="s">
+        <v>15</v>
+      </c>
+      <c r="B734">
+        <v>16763</v>
+      </c>
+      <c r="C734" t="s">
+        <v>16</v>
+      </c>
+      <c r="D734" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E734" t="s">
+        <v>2289</v>
+      </c>
+      <c r="F734" t="s">
+        <v>19</v>
+      </c>
+      <c r="G734" t="s">
+        <v>20</v>
+      </c>
+      <c r="H734" t="s">
+        <v>28</v>
+      </c>
+      <c r="I734" t="s">
+        <v>28</v>
+      </c>
+      <c r="J734" t="s">
+        <v>115</v>
+      </c>
+      <c r="K734" t="s">
+        <v>23</v>
+      </c>
+      <c r="L734" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M734" t="s">
+        <v>2290</v>
+      </c>
+      <c r="N734" s="3">
+        <v>46289</v>
+      </c>
+      <c r="O734" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="735" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A735" t="s">
+        <v>15</v>
+      </c>
+      <c r="B735">
+        <v>16763</v>
+      </c>
+      <c r="C735" t="s">
+        <v>16</v>
+      </c>
+      <c r="D735" s="4" t="s">
+        <v>2291</v>
+      </c>
+      <c r="E735" s="4" t="s">
+        <v>2292</v>
+      </c>
+      <c r="F735" t="s">
+        <v>19</v>
+      </c>
+      <c r="G735" t="s">
+        <v>20</v>
+      </c>
+      <c r="H735" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I735" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J735" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K735" t="s">
+        <v>23</v>
+      </c>
+      <c r="L735" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M735" s="4" t="s">
+        <v>2293</v>
+      </c>
+      <c r="N735" s="3">
+        <v>46291</v>
+      </c>
+      <c r="O735" t="s">
+        <v>486</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="D735:E735">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H735">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I735:J735">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M735">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0620EAC8-3779-4EF1-979F-03D7D70AC815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924E6D72-A7B9-4E69-999F-5F212EAE8A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8823" uniqueCount="2294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8919" uniqueCount="2318">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -6916,6 +6916,78 @@
   </si>
   <si>
     <t>JK09E9119</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH977296</t>
+  </si>
+  <si>
+    <t>K12NP7901227</t>
+  </si>
+  <si>
+    <t>JK22D7793</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH973960</t>
+  </si>
+  <si>
+    <t>K12NP7896124</t>
+  </si>
+  <si>
+    <t>JK01BF7958</t>
+  </si>
+  <si>
+    <t>MBHHWB13STHD59399</t>
+  </si>
+  <si>
+    <t>K12NP4998247</t>
+  </si>
+  <si>
+    <t>JK01BF8199</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ989558</t>
+  </si>
+  <si>
+    <t>K12NP7910354</t>
+  </si>
+  <si>
+    <t>JK01BF8126</t>
+  </si>
+  <si>
+    <t>MBHHWBC3STJD87878</t>
+  </si>
+  <si>
+    <t>Z12EP4016488</t>
+  </si>
+  <si>
+    <t>JK01BF8168</t>
+  </si>
+  <si>
+    <t>MBJTYKL1STH389754</t>
+  </si>
+  <si>
+    <t>K15CN8041456</t>
+  </si>
+  <si>
+    <t>JK04L4852</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH957913</t>
+  </si>
+  <si>
+    <t>K12NP7888010</t>
+  </si>
+  <si>
+    <t>JK13L0856</t>
+  </si>
+  <si>
+    <t>MBHKWD13STD861089</t>
+  </si>
+  <si>
+    <t>K12NP7827799</t>
+  </si>
+  <si>
+    <t>LA017478</t>
   </si>
 </sst>
 </file>
@@ -6931,12 +7003,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -6962,7 +7040,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6972,11 +7050,102 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -7307,24 +7476,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O735">
-  <autoFilter ref="A1:O735" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O743">
+  <autoFilter ref="A1:O743" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="27"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
-    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" totalsRowDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" totalsRowDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" totalsRowDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" totalsRowDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" totalsRowDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" totalsRowDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" totalsRowDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" totalsRowDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" totalsRowDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="6" totalsRowDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" totalsRowDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" totalsRowDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" totalsRowDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" totalsRowDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" totalsRowDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" totalsRowDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" totalsRowDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" totalsRowDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" totalsRowDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7627,7 +7796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O735"/>
+  <dimension ref="A1:O743"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -42191,23 +42360,439 @@
         <v>486</v>
       </c>
     </row>
+    <row r="736" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A736" t="s">
+        <v>15</v>
+      </c>
+      <c r="B736">
+        <v>16763</v>
+      </c>
+      <c r="C736" t="s">
+        <v>16</v>
+      </c>
+      <c r="D736" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E736" t="s">
+        <v>2295</v>
+      </c>
+      <c r="F736" t="s">
+        <v>19</v>
+      </c>
+      <c r="G736" t="s">
+        <v>20</v>
+      </c>
+      <c r="H736" t="s">
+        <v>53</v>
+      </c>
+      <c r="I736" t="s">
+        <v>53</v>
+      </c>
+      <c r="J736" t="s">
+        <v>29</v>
+      </c>
+      <c r="K736" t="s">
+        <v>23</v>
+      </c>
+      <c r="L736" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M736" t="s">
+        <v>2296</v>
+      </c>
+      <c r="N736" s="3">
+        <v>46291</v>
+      </c>
+      <c r="O736" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="737" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A737" t="s">
+        <v>15</v>
+      </c>
+      <c r="B737">
+        <v>16763</v>
+      </c>
+      <c r="C737" t="s">
+        <v>16</v>
+      </c>
+      <c r="D737" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E737" t="s">
+        <v>2298</v>
+      </c>
+      <c r="F737" t="s">
+        <v>19</v>
+      </c>
+      <c r="G737" t="s">
+        <v>20</v>
+      </c>
+      <c r="H737" t="s">
+        <v>53</v>
+      </c>
+      <c r="I737" t="s">
+        <v>53</v>
+      </c>
+      <c r="J737" t="s">
+        <v>54</v>
+      </c>
+      <c r="K737" t="s">
+        <v>23</v>
+      </c>
+      <c r="L737" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M737" t="s">
+        <v>2299</v>
+      </c>
+      <c r="N737" s="3">
+        <v>46291</v>
+      </c>
+      <c r="O737" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="738" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A738" t="s">
+        <v>15</v>
+      </c>
+      <c r="B738">
+        <v>16763</v>
+      </c>
+      <c r="C738" t="s">
+        <v>16</v>
+      </c>
+      <c r="D738" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E738" t="s">
+        <v>2301</v>
+      </c>
+      <c r="F738" t="s">
+        <v>19</v>
+      </c>
+      <c r="G738" t="s">
+        <v>20</v>
+      </c>
+      <c r="H738" t="s">
+        <v>28</v>
+      </c>
+      <c r="I738" t="s">
+        <v>28</v>
+      </c>
+      <c r="J738" t="s">
+        <v>29</v>
+      </c>
+      <c r="K738" t="s">
+        <v>23</v>
+      </c>
+      <c r="L738" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M738" t="s">
+        <v>2302</v>
+      </c>
+      <c r="N738" s="3">
+        <v>46293</v>
+      </c>
+      <c r="O738" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="739" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A739" t="s">
+        <v>15</v>
+      </c>
+      <c r="B739">
+        <v>16763</v>
+      </c>
+      <c r="C739" t="s">
+        <v>16</v>
+      </c>
+      <c r="D739" t="s">
+        <v>2303</v>
+      </c>
+      <c r="E739" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F739" t="s">
+        <v>19</v>
+      </c>
+      <c r="G739" t="s">
+        <v>20</v>
+      </c>
+      <c r="H739" t="s">
+        <v>40</v>
+      </c>
+      <c r="I739" t="s">
+        <v>40</v>
+      </c>
+      <c r="J739" t="s">
+        <v>74</v>
+      </c>
+      <c r="K739" t="s">
+        <v>23</v>
+      </c>
+      <c r="L739" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M739" t="s">
+        <v>2305</v>
+      </c>
+      <c r="N739" s="3">
+        <v>46293</v>
+      </c>
+      <c r="O739" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="740" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A740" t="s">
+        <v>15</v>
+      </c>
+      <c r="B740">
+        <v>16763</v>
+      </c>
+      <c r="C740" t="s">
+        <v>16</v>
+      </c>
+      <c r="D740" t="s">
+        <v>2306</v>
+      </c>
+      <c r="E740" t="s">
+        <v>2307</v>
+      </c>
+      <c r="F740" t="s">
+        <v>19</v>
+      </c>
+      <c r="G740" t="s">
+        <v>20</v>
+      </c>
+      <c r="H740" t="s">
+        <v>28</v>
+      </c>
+      <c r="I740" t="s">
+        <v>28</v>
+      </c>
+      <c r="J740" t="s">
+        <v>29</v>
+      </c>
+      <c r="K740" t="s">
+        <v>23</v>
+      </c>
+      <c r="L740" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M740" t="s">
+        <v>2308</v>
+      </c>
+      <c r="N740" s="3">
+        <v>46293</v>
+      </c>
+      <c r="O740" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="741" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A741" t="s">
+        <v>15</v>
+      </c>
+      <c r="B741">
+        <v>16763</v>
+      </c>
+      <c r="C741" t="s">
+        <v>16</v>
+      </c>
+      <c r="D741" s="4" t="s">
+        <v>2309</v>
+      </c>
+      <c r="E741" s="4" t="s">
+        <v>2310</v>
+      </c>
+      <c r="F741" t="s">
+        <v>19</v>
+      </c>
+      <c r="G741" t="s">
+        <v>20</v>
+      </c>
+      <c r="H741" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I741" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J741" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K741" t="s">
+        <v>1236</v>
+      </c>
+      <c r="L741" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M741" s="4" t="s">
+        <v>2311</v>
+      </c>
+      <c r="N741" s="3">
+        <v>46293</v>
+      </c>
+      <c r="O741" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="742" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A742" t="s">
+        <v>15</v>
+      </c>
+      <c r="B742">
+        <v>16763</v>
+      </c>
+      <c r="C742" t="s">
+        <v>16</v>
+      </c>
+      <c r="D742" s="5" t="s">
+        <v>2312</v>
+      </c>
+      <c r="E742" s="5" t="s">
+        <v>2313</v>
+      </c>
+      <c r="F742" t="s">
+        <v>19</v>
+      </c>
+      <c r="G742" t="s">
+        <v>20</v>
+      </c>
+      <c r="H742" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I742" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J742" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K742" t="s">
+        <v>23</v>
+      </c>
+      <c r="L742" s="2">
+        <v>46266</v>
+      </c>
+      <c r="M742" s="5" t="s">
+        <v>2314</v>
+      </c>
+      <c r="N742" s="3">
+        <v>46293</v>
+      </c>
+      <c r="O742" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="743" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A743" t="s">
+        <v>15</v>
+      </c>
+      <c r="B743">
+        <v>16763</v>
+      </c>
+      <c r="C743" t="s">
+        <v>16</v>
+      </c>
+      <c r="D743" s="5" t="s">
+        <v>2315</v>
+      </c>
+      <c r="E743" s="5" t="s">
+        <v>2316</v>
+      </c>
+      <c r="F743" t="s">
+        <v>19</v>
+      </c>
+      <c r="G743" t="s">
+        <v>20</v>
+      </c>
+      <c r="H743" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I743" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J743" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K743" t="s">
+        <v>23</v>
+      </c>
+      <c r="L743" s="2">
+        <v>46113</v>
+      </c>
+      <c r="M743" s="5" t="s">
+        <v>2317</v>
+      </c>
+      <c r="N743" s="3">
+        <v>46293</v>
+      </c>
+      <c r="O743" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="D735:E735">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H735">
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I735:J735">
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M735">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D741:E742">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H741:H742">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I741:J742">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D743:E743">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D743:E743">
+    <cfRule type="expression" dxfId="3" priority="5">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H743">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I735:J735">
+  <conditionalFormatting sqref="I743:J743">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M735">
+  <conditionalFormatting sqref="M743">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924E6D72-A7B9-4E69-999F-5F212EAE8A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74026313-F240-46FA-89F5-E9FF3A1ED677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8919" uniqueCount="2318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8967" uniqueCount="2330">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -6988,6 +6988,42 @@
   </si>
   <si>
     <t>LA017478</t>
+  </si>
+  <si>
+    <t>MBHHWB13STGD46351</t>
+  </si>
+  <si>
+    <t>K12NP4986593</t>
+  </si>
+  <si>
+    <t>JK01BF8629</t>
+  </si>
+  <si>
+    <t>MBHHWB13STGD36522</t>
+  </si>
+  <si>
+    <t>K12NP4977640</t>
+  </si>
+  <si>
+    <t>JK22D7848</t>
+  </si>
+  <si>
+    <t>MBJTYKL1STH389731</t>
+  </si>
+  <si>
+    <t>K15CN8042149</t>
+  </si>
+  <si>
+    <t>JK01BF8604</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ985844</t>
+  </si>
+  <si>
+    <t>K12NP7907549</t>
+  </si>
+  <si>
+    <t>JK01BF8652</t>
   </si>
 </sst>
 </file>
@@ -7003,21 +7039,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -7025,39 +7055,66 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="32">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -7476,24 +7533,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O743">
-  <autoFilter ref="A1:O743" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O747">
+  <autoFilter ref="A1:O747" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="31"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
-    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" totalsRowDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" totalsRowDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" totalsRowDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" totalsRowDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" totalsRowDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" totalsRowDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" totalsRowDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" totalsRowDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" totalsRowDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" totalsRowDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" totalsRowDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" totalsRowDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" totalsRowDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" totalsRowDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" totalsRowDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" totalsRowDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" totalsRowDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" totalsRowDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7796,7 +7853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O743"/>
+  <dimension ref="A1:O747"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -42323,10 +42380,10 @@
       <c r="C735" t="s">
         <v>16</v>
       </c>
-      <c r="D735" s="4" t="s">
+      <c r="D735" t="s">
         <v>2291</v>
       </c>
-      <c r="E735" s="4" t="s">
+      <c r="E735" t="s">
         <v>2292</v>
       </c>
       <c r="F735" t="s">
@@ -42335,13 +42392,13 @@
       <c r="G735" t="s">
         <v>20</v>
       </c>
-      <c r="H735" s="4" t="s">
+      <c r="H735" t="s">
         <v>28</v>
       </c>
-      <c r="I735" s="4" t="s">
+      <c r="I735" t="s">
         <v>28</v>
       </c>
-      <c r="J735" s="4" t="s">
+      <c r="J735" t="s">
         <v>29</v>
       </c>
       <c r="K735" t="s">
@@ -42350,7 +42407,7 @@
       <c r="L735" s="2">
         <v>46266</v>
       </c>
-      <c r="M735" s="4" t="s">
+      <c r="M735" t="s">
         <v>2293</v>
       </c>
       <c r="N735" s="3">
@@ -42605,10 +42662,10 @@
       <c r="C741" t="s">
         <v>16</v>
       </c>
-      <c r="D741" s="4" t="s">
+      <c r="D741" t="s">
         <v>2309</v>
       </c>
-      <c r="E741" s="4" t="s">
+      <c r="E741" t="s">
         <v>2310</v>
       </c>
       <c r="F741" t="s">
@@ -42617,13 +42674,13 @@
       <c r="G741" t="s">
         <v>20</v>
       </c>
-      <c r="H741" s="4" t="s">
+      <c r="H741" t="s">
         <v>111</v>
       </c>
-      <c r="I741" s="4" t="s">
+      <c r="I741" t="s">
         <v>111</v>
       </c>
-      <c r="J741" s="4" t="s">
+      <c r="J741" t="s">
         <v>45</v>
       </c>
       <c r="K741" t="s">
@@ -42632,7 +42689,7 @@
       <c r="L741" s="2">
         <v>46266</v>
       </c>
-      <c r="M741" s="4" t="s">
+      <c r="M741" t="s">
         <v>2311</v>
       </c>
       <c r="N741" s="3">
@@ -42652,10 +42709,10 @@
       <c r="C742" t="s">
         <v>16</v>
       </c>
-      <c r="D742" s="5" t="s">
+      <c r="D742" t="s">
         <v>2312</v>
       </c>
-      <c r="E742" s="5" t="s">
+      <c r="E742" t="s">
         <v>2313</v>
       </c>
       <c r="F742" t="s">
@@ -42664,13 +42721,13 @@
       <c r="G742" t="s">
         <v>20</v>
       </c>
-      <c r="H742" s="5" t="s">
+      <c r="H742" t="s">
         <v>40</v>
       </c>
-      <c r="I742" s="5" t="s">
+      <c r="I742" t="s">
         <v>40</v>
       </c>
-      <c r="J742" s="5" t="s">
+      <c r="J742" t="s">
         <v>74</v>
       </c>
       <c r="K742" t="s">
@@ -42679,7 +42736,7 @@
       <c r="L742" s="2">
         <v>46266</v>
       </c>
-      <c r="M742" s="5" t="s">
+      <c r="M742" t="s">
         <v>2314</v>
       </c>
       <c r="N742" s="3">
@@ -42699,10 +42756,10 @@
       <c r="C743" t="s">
         <v>16</v>
       </c>
-      <c r="D743" s="5" t="s">
+      <c r="D743" t="s">
         <v>2315</v>
       </c>
-      <c r="E743" s="5" t="s">
+      <c r="E743" t="s">
         <v>2316</v>
       </c>
       <c r="F743" t="s">
@@ -42711,13 +42768,13 @@
       <c r="G743" t="s">
         <v>20</v>
       </c>
-      <c r="H743" s="5" t="s">
+      <c r="H743" t="s">
         <v>40</v>
       </c>
-      <c r="I743" s="5" t="s">
+      <c r="I743" t="s">
         <v>40</v>
       </c>
-      <c r="J743" s="5" t="s">
+      <c r="J743" t="s">
         <v>29</v>
       </c>
       <c r="K743" t="s">
@@ -42726,7 +42783,7 @@
       <c r="L743" s="2">
         <v>46113</v>
       </c>
-      <c r="M743" s="5" t="s">
+      <c r="M743" t="s">
         <v>2317</v>
       </c>
       <c r="N743" s="3">
@@ -42736,67 +42793,195 @@
         <v>25</v>
       </c>
     </row>
+    <row r="744" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A744" t="s">
+        <v>15</v>
+      </c>
+      <c r="B744">
+        <v>16763</v>
+      </c>
+      <c r="C744" t="s">
+        <v>16</v>
+      </c>
+      <c r="D744" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E744" t="s">
+        <v>2319</v>
+      </c>
+      <c r="F744" t="s">
+        <v>19</v>
+      </c>
+      <c r="G744" t="s">
+        <v>20</v>
+      </c>
+      <c r="H744" t="s">
+        <v>201</v>
+      </c>
+      <c r="I744" t="s">
+        <v>201</v>
+      </c>
+      <c r="J744" t="s">
+        <v>74</v>
+      </c>
+      <c r="K744" t="s">
+        <v>23</v>
+      </c>
+      <c r="L744" s="2">
+        <v>46204</v>
+      </c>
+      <c r="M744" t="s">
+        <v>2320</v>
+      </c>
+      <c r="N744" s="3">
+        <v>46298</v>
+      </c>
+      <c r="O744" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="745" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A745" t="s">
+        <v>15</v>
+      </c>
+      <c r="B745">
+        <v>16763</v>
+      </c>
+      <c r="C745" t="s">
+        <v>16</v>
+      </c>
+      <c r="D745" t="s">
+        <v>2321</v>
+      </c>
+      <c r="E745" t="s">
+        <v>2322</v>
+      </c>
+      <c r="F745" t="s">
+        <v>19</v>
+      </c>
+      <c r="G745" t="s">
+        <v>20</v>
+      </c>
+      <c r="H745" t="s">
+        <v>28</v>
+      </c>
+      <c r="I745" t="s">
+        <v>28</v>
+      </c>
+      <c r="J745" t="s">
+        <v>29</v>
+      </c>
+      <c r="K745" t="s">
+        <v>23</v>
+      </c>
+      <c r="L745" s="2">
+        <v>46204</v>
+      </c>
+      <c r="M745" t="s">
+        <v>2323</v>
+      </c>
+      <c r="N745" s="3">
+        <v>46298</v>
+      </c>
+      <c r="O745" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="746" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A746" t="s">
+        <v>15</v>
+      </c>
+      <c r="B746">
+        <v>16763</v>
+      </c>
+      <c r="C746" t="s">
+        <v>16</v>
+      </c>
+      <c r="D746" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E746" t="s">
+        <v>2325</v>
+      </c>
+      <c r="F746" t="s">
+        <v>19</v>
+      </c>
+      <c r="G746" t="s">
+        <v>20</v>
+      </c>
+      <c r="H746" t="s">
+        <v>111</v>
+      </c>
+      <c r="I746" t="s">
+        <v>111</v>
+      </c>
+      <c r="J746" t="s">
+        <v>29</v>
+      </c>
+      <c r="K746" t="s">
+        <v>46</v>
+      </c>
+      <c r="L746" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M746" t="s">
+        <v>2326</v>
+      </c>
+      <c r="N746" s="3">
+        <v>46298</v>
+      </c>
+      <c r="O746" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="747" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A747" t="s">
+        <v>15</v>
+      </c>
+      <c r="B747">
+        <v>16763</v>
+      </c>
+      <c r="C747" t="s">
+        <v>16</v>
+      </c>
+      <c r="D747" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E747" t="s">
+        <v>2328</v>
+      </c>
+      <c r="F747" t="s">
+        <v>19</v>
+      </c>
+      <c r="G747" t="s">
+        <v>20</v>
+      </c>
+      <c r="H747" t="s">
+        <v>53</v>
+      </c>
+      <c r="I747" t="s">
+        <v>53</v>
+      </c>
+      <c r="J747" t="s">
+        <v>54</v>
+      </c>
+      <c r="K747" t="s">
+        <v>23</v>
+      </c>
+      <c r="L747" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M747" t="s">
+        <v>2329</v>
+      </c>
+      <c r="N747" s="3">
+        <v>46298</v>
+      </c>
+      <c r="O747" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D735:E735">
-    <cfRule type="expression" dxfId="11" priority="12">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H735">
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I735:J735">
-    <cfRule type="expression" dxfId="9" priority="10">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M735">
-    <cfRule type="expression" dxfId="8" priority="9">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D741:E742">
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H741:H742">
-    <cfRule type="expression" dxfId="6" priority="7">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I741:J742">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D743:E743">
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D743:E743">
-    <cfRule type="expression" dxfId="3" priority="5">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H743">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I743:J743">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M743">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74026313-F240-46FA-89F5-E9FF3A1ED677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C854D8-504C-4E62-9016-C1D7DF18A466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8967" uniqueCount="2330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9003" uniqueCount="2339">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7024,6 +7024,33 @@
   </si>
   <si>
     <t>JK01BF8652</t>
+  </si>
+  <si>
+    <t>MBHHWB13STEC95417</t>
+  </si>
+  <si>
+    <t>K12NP4940727</t>
+  </si>
+  <si>
+    <t>JK05R0606</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ984953</t>
+  </si>
+  <si>
+    <t>K12NP7906944</t>
+  </si>
+  <si>
+    <t>JK01BF8736</t>
+  </si>
+  <si>
+    <t>MBJTYKL1STJ394825</t>
+  </si>
+  <si>
+    <t>K15CN8056681</t>
+  </si>
+  <si>
+    <t>JK01BF8798</t>
   </si>
 </sst>
 </file>
@@ -7070,183 +7097,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <b val="0"/>
@@ -7533,24 +7384,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O747">
-  <autoFilter ref="A1:O747" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O750">
+  <autoFilter ref="A1:O750" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="15"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
-    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" totalsRowDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" totalsRowDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" totalsRowDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" totalsRowDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" totalsRowDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" totalsRowDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" totalsRowDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" totalsRowDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" totalsRowDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" totalsRowDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" totalsRowDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" totalsRowDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" totalsRowDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" totalsRowDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" totalsRowDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" totalsRowDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" totalsRowDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" totalsRowDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="2" totalsRowDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7853,7 +7704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O747"/>
+  <dimension ref="A1:O750"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -42981,6 +42832,147 @@
         <v>25</v>
       </c>
     </row>
+    <row r="748" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A748" t="s">
+        <v>15</v>
+      </c>
+      <c r="B748">
+        <v>16763</v>
+      </c>
+      <c r="C748" t="s">
+        <v>16</v>
+      </c>
+      <c r="D748" t="s">
+        <v>2330</v>
+      </c>
+      <c r="E748" t="s">
+        <v>2331</v>
+      </c>
+      <c r="F748" t="s">
+        <v>19</v>
+      </c>
+      <c r="G748" t="s">
+        <v>20</v>
+      </c>
+      <c r="H748" t="s">
+        <v>162</v>
+      </c>
+      <c r="I748" t="s">
+        <v>162</v>
+      </c>
+      <c r="J748" t="s">
+        <v>29</v>
+      </c>
+      <c r="K748" t="s">
+        <v>23</v>
+      </c>
+      <c r="L748" s="2">
+        <v>46174</v>
+      </c>
+      <c r="M748" t="s">
+        <v>2332</v>
+      </c>
+      <c r="N748" s="3">
+        <v>46300</v>
+      </c>
+      <c r="O748" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="749" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A749" t="s">
+        <v>15</v>
+      </c>
+      <c r="B749">
+        <v>16763</v>
+      </c>
+      <c r="C749" t="s">
+        <v>16</v>
+      </c>
+      <c r="D749" t="s">
+        <v>2333</v>
+      </c>
+      <c r="E749" t="s">
+        <v>2334</v>
+      </c>
+      <c r="F749" t="s">
+        <v>19</v>
+      </c>
+      <c r="G749" t="s">
+        <v>20</v>
+      </c>
+      <c r="H749" t="s">
+        <v>53</v>
+      </c>
+      <c r="I749" t="s">
+        <v>53</v>
+      </c>
+      <c r="J749" t="s">
+        <v>54</v>
+      </c>
+      <c r="K749" t="s">
+        <v>23</v>
+      </c>
+      <c r="L749" s="2">
+        <v>46174</v>
+      </c>
+      <c r="M749" t="s">
+        <v>2335</v>
+      </c>
+      <c r="N749" s="3">
+        <v>46300</v>
+      </c>
+      <c r="O749" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="750" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A750" t="s">
+        <v>15</v>
+      </c>
+      <c r="B750">
+        <v>16763</v>
+      </c>
+      <c r="C750" t="s">
+        <v>16</v>
+      </c>
+      <c r="D750" t="s">
+        <v>2336</v>
+      </c>
+      <c r="E750" t="s">
+        <v>2337</v>
+      </c>
+      <c r="F750" t="s">
+        <v>19</v>
+      </c>
+      <c r="G750" t="s">
+        <v>20</v>
+      </c>
+      <c r="H750" t="s">
+        <v>111</v>
+      </c>
+      <c r="I750" t="s">
+        <v>111</v>
+      </c>
+      <c r="J750" t="s">
+        <v>45</v>
+      </c>
+      <c r="K750" t="s">
+        <v>46</v>
+      </c>
+      <c r="L750" s="2">
+        <v>46174</v>
+      </c>
+      <c r="M750" t="s">
+        <v>2338</v>
+      </c>
+      <c r="N750" s="3">
+        <v>46300</v>
+      </c>
+      <c r="O750" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C854D8-504C-4E62-9016-C1D7DF18A466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F5AC19-C2ED-4002-BE3A-4946AB4709FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9003" uniqueCount="2339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9051" uniqueCount="2351">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7051,6 +7051,42 @@
   </si>
   <si>
     <t>JK01BF8798</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH977223</t>
+  </si>
+  <si>
+    <t>K12NP7901190</t>
+  </si>
+  <si>
+    <t>JK13L1153</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ995453</t>
+  </si>
+  <si>
+    <t>K12NP7914675</t>
+  </si>
+  <si>
+    <t>JK13L1120</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ985442</t>
+  </si>
+  <si>
+    <t>K12NP7907321</t>
+  </si>
+  <si>
+    <t>JK13L1196</t>
+  </si>
+  <si>
+    <t>MBHHWB13STHD69695</t>
+  </si>
+  <si>
+    <t>K12NP5007422</t>
+  </si>
+  <si>
+    <t>JK04L5090</t>
   </si>
 </sst>
 </file>
@@ -7384,8 +7420,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O750">
-  <autoFilter ref="A1:O750" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O754">
+  <autoFilter ref="A1:O754" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="15"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -7704,7 +7740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O750"/>
+  <dimension ref="A1:O754"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -42973,6 +43009,194 @@
         <v>25</v>
       </c>
     </row>
+    <row r="751" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A751" t="s">
+        <v>15</v>
+      </c>
+      <c r="B751">
+        <v>16763</v>
+      </c>
+      <c r="C751" t="s">
+        <v>16</v>
+      </c>
+      <c r="D751" t="s">
+        <v>2339</v>
+      </c>
+      <c r="E751" t="s">
+        <v>2340</v>
+      </c>
+      <c r="F751" t="s">
+        <v>19</v>
+      </c>
+      <c r="G751" t="s">
+        <v>20</v>
+      </c>
+      <c r="H751" t="s">
+        <v>53</v>
+      </c>
+      <c r="I751" t="s">
+        <v>53</v>
+      </c>
+      <c r="J751" t="s">
+        <v>29</v>
+      </c>
+      <c r="K751" t="s">
+        <v>23</v>
+      </c>
+      <c r="L751" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M751" t="s">
+        <v>2341</v>
+      </c>
+      <c r="N751" s="3">
+        <v>46301</v>
+      </c>
+      <c r="O751" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="752" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A752" t="s">
+        <v>15</v>
+      </c>
+      <c r="B752">
+        <v>16763</v>
+      </c>
+      <c r="C752" t="s">
+        <v>16</v>
+      </c>
+      <c r="D752" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E752" t="s">
+        <v>2343</v>
+      </c>
+      <c r="F752" t="s">
+        <v>19</v>
+      </c>
+      <c r="G752" t="s">
+        <v>20</v>
+      </c>
+      <c r="H752" t="s">
+        <v>53</v>
+      </c>
+      <c r="I752" t="s">
+        <v>53</v>
+      </c>
+      <c r="J752" t="s">
+        <v>1784</v>
+      </c>
+      <c r="K752" t="s">
+        <v>23</v>
+      </c>
+      <c r="L752" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M752" t="s">
+        <v>2344</v>
+      </c>
+      <c r="N752" s="3">
+        <v>46301</v>
+      </c>
+      <c r="O752" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="753" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A753" t="s">
+        <v>15</v>
+      </c>
+      <c r="B753">
+        <v>16763</v>
+      </c>
+      <c r="C753" t="s">
+        <v>16</v>
+      </c>
+      <c r="D753" t="s">
+        <v>2345</v>
+      </c>
+      <c r="E753" t="s">
+        <v>2346</v>
+      </c>
+      <c r="F753" t="s">
+        <v>19</v>
+      </c>
+      <c r="G753" t="s">
+        <v>20</v>
+      </c>
+      <c r="H753" t="s">
+        <v>53</v>
+      </c>
+      <c r="I753" t="s">
+        <v>53</v>
+      </c>
+      <c r="J753" t="s">
+        <v>54</v>
+      </c>
+      <c r="K753" t="s">
+        <v>23</v>
+      </c>
+      <c r="L753" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M753" t="s">
+        <v>2347</v>
+      </c>
+      <c r="N753" s="3">
+        <v>46301</v>
+      </c>
+      <c r="O753" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="754" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A754" t="s">
+        <v>15</v>
+      </c>
+      <c r="B754">
+        <v>16763</v>
+      </c>
+      <c r="C754" t="s">
+        <v>16</v>
+      </c>
+      <c r="D754" t="s">
+        <v>2348</v>
+      </c>
+      <c r="E754" t="s">
+        <v>2349</v>
+      </c>
+      <c r="F754" t="s">
+        <v>19</v>
+      </c>
+      <c r="G754" t="s">
+        <v>20</v>
+      </c>
+      <c r="H754" t="s">
+        <v>162</v>
+      </c>
+      <c r="I754" t="s">
+        <v>162</v>
+      </c>
+      <c r="J754" t="s">
+        <v>29</v>
+      </c>
+      <c r="K754" t="s">
+        <v>23</v>
+      </c>
+      <c r="L754" s="2">
+        <v>46235</v>
+      </c>
+      <c r="M754" t="s">
+        <v>2350</v>
+      </c>
+      <c r="N754" s="3">
+        <v>46301</v>
+      </c>
+      <c r="O754" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F5AC19-C2ED-4002-BE3A-4946AB4709FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0626D2-2580-4CF8-BDB5-CB8DDCE40387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9051" uniqueCount="2351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9087" uniqueCount="2360">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7087,6 +7087,33 @@
   </si>
   <si>
     <t>JK04L5090</t>
+  </si>
+  <si>
+    <t>MBJTYKL1STG382980</t>
+  </si>
+  <si>
+    <t>K15CN8014222</t>
+  </si>
+  <si>
+    <t>JK01BF9079</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ985668</t>
+  </si>
+  <si>
+    <t>K12NP7907437</t>
+  </si>
+  <si>
+    <t>JK01BF9214</t>
+  </si>
+  <si>
+    <t>MBJTYKL1STJ395578</t>
+  </si>
+  <si>
+    <t>K15CN8058189</t>
+  </si>
+  <si>
+    <t>JK22D7978</t>
   </si>
 </sst>
 </file>
@@ -7102,15 +7129,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -7118,22 +7151,83 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -7420,24 +7514,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O754">
-  <autoFilter ref="A1:O754" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O757">
+  <autoFilter ref="A1:O757" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
-    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" totalsRowDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" totalsRowDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" totalsRowDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" totalsRowDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" totalsRowDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" totalsRowDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" totalsRowDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" totalsRowDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" totalsRowDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="2" totalsRowDxfId="1"/>
-    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{E9F89ECC-6A75-4413-8CEC-2CF7D3970F9B}" name="LOC CD" totalsRowDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{F2CBECE1-B668-4D7A-9DF1-1AF43CC19C33}" name="VIN" totalsRowDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{8309068C-D1A3-41A3-B61D-031F8A4A5306}" name="ENGINE NUM" totalsRowDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{0C65D2FB-F686-4E5C-9202-5018FF73BF32}" name="ORDER TYPE" totalsRowDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{C58385E4-FAD5-48F8-ADA6-17A38AAA0053}" name="VEHICLE CATEGORY" totalsRowDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{FD624D60-E237-4E07-8A3D-A0DF15B9BF9C}" name="MODEL" totalsRowDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" totalsRowDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" totalsRowDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" totalsRowDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7740,7 +7834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O754"/>
+  <dimension ref="A1:O757"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -43197,7 +43291,168 @@
         <v>25</v>
       </c>
     </row>
+    <row r="755" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A755" t="s">
+        <v>15</v>
+      </c>
+      <c r="B755">
+        <v>16763</v>
+      </c>
+      <c r="C755" t="s">
+        <v>16</v>
+      </c>
+      <c r="D755" t="s">
+        <v>2351</v>
+      </c>
+      <c r="E755" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F755" t="s">
+        <v>19</v>
+      </c>
+      <c r="G755" t="s">
+        <v>20</v>
+      </c>
+      <c r="H755" t="s">
+        <v>111</v>
+      </c>
+      <c r="I755" t="s">
+        <v>111</v>
+      </c>
+      <c r="J755" t="s">
+        <v>115</v>
+      </c>
+      <c r="K755" t="s">
+        <v>46</v>
+      </c>
+      <c r="L755" s="2">
+        <v>46204</v>
+      </c>
+      <c r="M755" t="s">
+        <v>2353</v>
+      </c>
+      <c r="N755" s="3">
+        <v>46303</v>
+      </c>
+      <c r="O755" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="756" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A756" t="s">
+        <v>15</v>
+      </c>
+      <c r="B756">
+        <v>16763</v>
+      </c>
+      <c r="C756" t="s">
+        <v>16</v>
+      </c>
+      <c r="D756" s="4" t="s">
+        <v>2354</v>
+      </c>
+      <c r="E756" s="4" t="s">
+        <v>2355</v>
+      </c>
+      <c r="F756" t="s">
+        <v>19</v>
+      </c>
+      <c r="G756" t="s">
+        <v>20</v>
+      </c>
+      <c r="H756" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I756" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J756" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K756" t="s">
+        <v>23</v>
+      </c>
+      <c r="L756" s="2">
+        <v>46204</v>
+      </c>
+      <c r="M756" s="4" t="s">
+        <v>2356</v>
+      </c>
+      <c r="N756" s="3">
+        <v>46304</v>
+      </c>
+      <c r="O756" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="757" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A757" t="s">
+        <v>15</v>
+      </c>
+      <c r="B757">
+        <v>16763</v>
+      </c>
+      <c r="C757" t="s">
+        <v>16</v>
+      </c>
+      <c r="D757" s="5" t="s">
+        <v>2357</v>
+      </c>
+      <c r="E757" s="5" t="s">
+        <v>2358</v>
+      </c>
+      <c r="F757" t="s">
+        <v>19</v>
+      </c>
+      <c r="G757" t="s">
+        <v>20</v>
+      </c>
+      <c r="H757" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I757" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="J757" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K757" t="s">
+        <v>46</v>
+      </c>
+      <c r="L757" s="2">
+        <v>46204</v>
+      </c>
+      <c r="M757" s="5" t="s">
+        <v>2359</v>
+      </c>
+      <c r="N757" s="3">
+        <v>46304</v>
+      </c>
+      <c r="O757" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="D756:E757">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H756:H757">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I756:J757">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M756:M757">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8888A9-7A17-45BF-B4AB-E883A14566DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51938029-0E25-45A0-9AF7-34445C6D7978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9099" uniqueCount="2363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9135" uniqueCount="2372">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7123,6 +7123,33 @@
   </si>
   <si>
     <t>JK04L7210</t>
+  </si>
+  <si>
+    <t>JK04L5386</t>
+  </si>
+  <si>
+    <t>K12NP7914575</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ997671</t>
+  </si>
+  <si>
+    <t>MA3EDC03TTH411878</t>
+  </si>
+  <si>
+    <t>K12NN4686451</t>
+  </si>
+  <si>
+    <t>JK01BF9179</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ997516</t>
+  </si>
+  <si>
+    <t>K12NP7916101</t>
+  </si>
+  <si>
+    <t>JK13L9111</t>
   </si>
 </sst>
 </file>
@@ -7167,12 +7194,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="20">
-    <dxf>
-      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -7256,6 +7277,9 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -7292,6 +7316,9 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -7497,8 +7524,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O758">
-  <autoFilter ref="A1:O758" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O761">
+  <autoFilter ref="A1:O761" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -7511,10 +7538,10 @@
     <tableColumn id="9" xr3:uid="{B6FAD2FA-A246-4195-924D-1102FDCB1393}" name="VARIANT" totalsRowDxfId="12"/>
     <tableColumn id="10" xr3:uid="{6938A859-96A0-4AE1-9A4E-F4674F3A61B7}" name="COLOR" totalsRowDxfId="11"/>
     <tableColumn id="11" xr3:uid="{AB6713D4-28A1-4475-AB39-29972293BE3C}" name="FUEL" totalsRowDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="1" totalsRowDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="0" totalsRowDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{B411678A-BBAC-4159-9F25-77BB1EFEC375}" name="MFG DATE" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{24A3F3EB-BAAC-42C1-88DC-60A80F5C4A6C}" name="REG NUM" totalsRowDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{FDA381C7-81E5-4A1D-8975-52C0E469CF2A}" name="DATE OF REG (DD-MON-YYYY)" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{03CC8BE8-8064-482D-9D34-11C2F16733CC}" name="VEHICLE CLASS (P/C)" totalsRowFunction="count" totalsRowDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7817,7 +7844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O758"/>
+  <dimension ref="A1:O761"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -43462,24 +43489,165 @@
         <v>25</v>
       </c>
     </row>
+    <row r="759" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A759" t="s">
+        <v>15</v>
+      </c>
+      <c r="B759">
+        <v>16763</v>
+      </c>
+      <c r="C759" t="s">
+        <v>16</v>
+      </c>
+      <c r="D759" t="s">
+        <v>2365</v>
+      </c>
+      <c r="E759" t="s">
+        <v>2364</v>
+      </c>
+      <c r="F759" t="s">
+        <v>19</v>
+      </c>
+      <c r="G759" t="s">
+        <v>20</v>
+      </c>
+      <c r="H759" t="s">
+        <v>40</v>
+      </c>
+      <c r="I759" t="s">
+        <v>40</v>
+      </c>
+      <c r="J759" t="s">
+        <v>74</v>
+      </c>
+      <c r="K759" t="s">
+        <v>23</v>
+      </c>
+      <c r="L759" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M759" t="s">
+        <v>2363</v>
+      </c>
+      <c r="N759" s="2">
+        <v>46310</v>
+      </c>
+      <c r="O759" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="760" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A760" t="s">
+        <v>15</v>
+      </c>
+      <c r="B760">
+        <v>16763</v>
+      </c>
+      <c r="C760" t="s">
+        <v>16</v>
+      </c>
+      <c r="D760" t="s">
+        <v>2366</v>
+      </c>
+      <c r="E760" t="s">
+        <v>2367</v>
+      </c>
+      <c r="F760" t="s">
+        <v>19</v>
+      </c>
+      <c r="G760" t="s">
+        <v>20</v>
+      </c>
+      <c r="H760" t="s">
+        <v>727</v>
+      </c>
+      <c r="I760" t="s">
+        <v>727</v>
+      </c>
+      <c r="J760" t="s">
+        <v>728</v>
+      </c>
+      <c r="K760" t="s">
+        <v>23</v>
+      </c>
+      <c r="L760" s="1">
+        <v>46235</v>
+      </c>
+      <c r="M760" t="s">
+        <v>2368</v>
+      </c>
+      <c r="N760" s="2">
+        <v>46304</v>
+      </c>
+      <c r="O760" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="761" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A761" t="s">
+        <v>15</v>
+      </c>
+      <c r="B761">
+        <v>16763</v>
+      </c>
+      <c r="C761" t="s">
+        <v>16</v>
+      </c>
+      <c r="D761" t="s">
+        <v>2369</v>
+      </c>
+      <c r="E761" t="s">
+        <v>2370</v>
+      </c>
+      <c r="F761" t="s">
+        <v>19</v>
+      </c>
+      <c r="G761" t="s">
+        <v>20</v>
+      </c>
+      <c r="H761" t="s">
+        <v>40</v>
+      </c>
+      <c r="I761" t="s">
+        <v>40</v>
+      </c>
+      <c r="J761" t="s">
+        <v>74</v>
+      </c>
+      <c r="K761" t="s">
+        <v>23</v>
+      </c>
+      <c r="L761" s="1">
+        <v>46235</v>
+      </c>
+      <c r="M761" t="s">
+        <v>2371</v>
+      </c>
+      <c r="N761" s="2">
+        <v>46310</v>
+      </c>
+      <c r="O761" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="D756:E757">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H756:H757">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I756:J757">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M756:M757">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51938029-0E25-45A0-9AF7-34445C6D7978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4306C042-AFD0-46B0-9F99-72800189B0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9135" uniqueCount="2372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9231" uniqueCount="2397">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7150,6 +7150,81 @@
   </si>
   <si>
     <t>JK13L9111</t>
+  </si>
+  <si>
+    <t>MBHKWD13STKA13482</t>
+  </si>
+  <si>
+    <t>K12NP7925803</t>
+  </si>
+  <si>
+    <t>JK13L1335</t>
+  </si>
+  <si>
+    <t>MBHKWD43STJ987045</t>
+  </si>
+  <si>
+    <t>K10CP7075578</t>
+  </si>
+  <si>
+    <t>FRONX TURBO S. HYBRID ALPHA</t>
+  </si>
+  <si>
+    <t>JK01BF9773</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ985806</t>
+  </si>
+  <si>
+    <t>K12NP7907527</t>
+  </si>
+  <si>
+    <t>JK01BF9723</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJA01278</t>
+  </si>
+  <si>
+    <t>K12NP7918582</t>
+  </si>
+  <si>
+    <t>JK01BF9734</t>
+  </si>
+  <si>
+    <t>26BH5359S</t>
+  </si>
+  <si>
+    <t>K15CN8028627</t>
+  </si>
+  <si>
+    <t>MBJTYKL1STG386026</t>
+  </si>
+  <si>
+    <t>JK05R2366</t>
+  </si>
+  <si>
+    <t>K12NP1698889</t>
+  </si>
+  <si>
+    <t>MBHKWD13STKA13009</t>
+  </si>
+  <si>
+    <t>JK09E9358</t>
+  </si>
+  <si>
+    <t>K12NP4997474</t>
+  </si>
+  <si>
+    <t>MBHHWB13STHD58472</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJA01185</t>
+  </si>
+  <si>
+    <t>K12NP7918544</t>
+  </si>
+  <si>
+    <t>JK15D0178</t>
   </si>
 </sst>
 </file>
@@ -7524,8 +7599,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O761">
-  <autoFilter ref="A1:O761" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O769">
+  <autoFilter ref="A1:O769" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -7844,7 +7919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O761"/>
+  <dimension ref="A1:O769"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -43627,6 +43702,382 @@
         <v>46310</v>
       </c>
       <c r="O761" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="762" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A762" t="s">
+        <v>15</v>
+      </c>
+      <c r="B762">
+        <v>16763</v>
+      </c>
+      <c r="C762" t="s">
+        <v>16</v>
+      </c>
+      <c r="D762" t="s">
+        <v>2372</v>
+      </c>
+      <c r="E762" t="s">
+        <v>2373</v>
+      </c>
+      <c r="F762" t="s">
+        <v>19</v>
+      </c>
+      <c r="G762" t="s">
+        <v>20</v>
+      </c>
+      <c r="H762" t="s">
+        <v>40</v>
+      </c>
+      <c r="I762" t="s">
+        <v>40</v>
+      </c>
+      <c r="J762" t="s">
+        <v>115</v>
+      </c>
+      <c r="K762" t="s">
+        <v>23</v>
+      </c>
+      <c r="L762" s="1">
+        <v>46235</v>
+      </c>
+      <c r="M762" t="s">
+        <v>2374</v>
+      </c>
+      <c r="N762" s="2">
+        <v>46310</v>
+      </c>
+      <c r="O762" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="763" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A763" t="s">
+        <v>15</v>
+      </c>
+      <c r="B763">
+        <v>16763</v>
+      </c>
+      <c r="C763" t="s">
+        <v>16</v>
+      </c>
+      <c r="D763" t="s">
+        <v>2375</v>
+      </c>
+      <c r="E763" t="s">
+        <v>2376</v>
+      </c>
+      <c r="F763" t="s">
+        <v>19</v>
+      </c>
+      <c r="G763" t="s">
+        <v>20</v>
+      </c>
+      <c r="H763" t="s">
+        <v>2377</v>
+      </c>
+      <c r="I763" t="s">
+        <v>2377</v>
+      </c>
+      <c r="J763" t="s">
+        <v>54</v>
+      </c>
+      <c r="K763" t="s">
+        <v>46</v>
+      </c>
+      <c r="L763" s="1">
+        <v>46235</v>
+      </c>
+      <c r="M763" t="s">
+        <v>2378</v>
+      </c>
+      <c r="N763" s="2">
+        <v>46310</v>
+      </c>
+      <c r="O763" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="764" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A764" t="s">
+        <v>15</v>
+      </c>
+      <c r="B764">
+        <v>16763</v>
+      </c>
+      <c r="C764" t="s">
+        <v>16</v>
+      </c>
+      <c r="D764" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E764" t="s">
+        <v>2380</v>
+      </c>
+      <c r="F764" t="s">
+        <v>19</v>
+      </c>
+      <c r="G764" t="s">
+        <v>20</v>
+      </c>
+      <c r="H764" t="s">
+        <v>53</v>
+      </c>
+      <c r="I764" t="s">
+        <v>53</v>
+      </c>
+      <c r="J764" t="s">
+        <v>53</v>
+      </c>
+      <c r="K764" t="s">
+        <v>23</v>
+      </c>
+      <c r="L764" s="1">
+        <v>46235</v>
+      </c>
+      <c r="M764" t="s">
+        <v>2381</v>
+      </c>
+      <c r="N764" s="2">
+        <v>46310</v>
+      </c>
+      <c r="O764" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="765" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A765" t="s">
+        <v>15</v>
+      </c>
+      <c r="B765">
+        <v>16763</v>
+      </c>
+      <c r="C765" t="s">
+        <v>16</v>
+      </c>
+      <c r="D765" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E765" t="s">
+        <v>2383</v>
+      </c>
+      <c r="F765" t="s">
+        <v>19</v>
+      </c>
+      <c r="G765" t="s">
+        <v>20</v>
+      </c>
+      <c r="H765" t="s">
+        <v>40</v>
+      </c>
+      <c r="I765" t="s">
+        <v>40</v>
+      </c>
+      <c r="J765" t="s">
+        <v>29</v>
+      </c>
+      <c r="K765" t="s">
+        <v>23</v>
+      </c>
+      <c r="L765" s="1">
+        <v>46235</v>
+      </c>
+      <c r="M765" t="s">
+        <v>2384</v>
+      </c>
+      <c r="N765" s="2">
+        <v>46310</v>
+      </c>
+      <c r="O765" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="766" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A766" t="s">
+        <v>15</v>
+      </c>
+      <c r="B766">
+        <v>16763</v>
+      </c>
+      <c r="C766" t="s">
+        <v>16</v>
+      </c>
+      <c r="D766" t="s">
+        <v>2393</v>
+      </c>
+      <c r="E766" t="s">
+        <v>2392</v>
+      </c>
+      <c r="F766" t="s">
+        <v>19</v>
+      </c>
+      <c r="G766" t="s">
+        <v>20</v>
+      </c>
+      <c r="H766" t="s">
+        <v>162</v>
+      </c>
+      <c r="I766" t="s">
+        <v>162</v>
+      </c>
+      <c r="J766" t="s">
+        <v>29</v>
+      </c>
+      <c r="K766" t="s">
+        <v>23</v>
+      </c>
+      <c r="L766" s="1">
+        <v>46235</v>
+      </c>
+      <c r="M766" t="s">
+        <v>2391</v>
+      </c>
+      <c r="N766" s="2">
+        <v>46311</v>
+      </c>
+      <c r="O766" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="767" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A767" t="s">
+        <v>15</v>
+      </c>
+      <c r="B767">
+        <v>16763</v>
+      </c>
+      <c r="C767" t="s">
+        <v>16</v>
+      </c>
+      <c r="D767" t="s">
+        <v>2390</v>
+      </c>
+      <c r="E767" t="s">
+        <v>2389</v>
+      </c>
+      <c r="F767" t="s">
+        <v>19</v>
+      </c>
+      <c r="G767" t="s">
+        <v>20</v>
+      </c>
+      <c r="H767" t="s">
+        <v>40</v>
+      </c>
+      <c r="I767" t="s">
+        <v>40</v>
+      </c>
+      <c r="J767" t="s">
+        <v>115</v>
+      </c>
+      <c r="K767" t="s">
+        <v>23</v>
+      </c>
+      <c r="L767" s="1">
+        <v>46235</v>
+      </c>
+      <c r="M767" t="s">
+        <v>2388</v>
+      </c>
+      <c r="N767" s="2">
+        <v>46311</v>
+      </c>
+      <c r="O767" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="768" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A768" t="s">
+        <v>15</v>
+      </c>
+      <c r="B768">
+        <v>16763</v>
+      </c>
+      <c r="C768" t="s">
+        <v>16</v>
+      </c>
+      <c r="D768" t="s">
+        <v>2387</v>
+      </c>
+      <c r="E768" t="s">
+        <v>2386</v>
+      </c>
+      <c r="F768" t="s">
+        <v>19</v>
+      </c>
+      <c r="G768" t="s">
+        <v>20</v>
+      </c>
+      <c r="H768" t="s">
+        <v>44</v>
+      </c>
+      <c r="I768" t="s">
+        <v>44</v>
+      </c>
+      <c r="J768" t="s">
+        <v>29</v>
+      </c>
+      <c r="K768" t="s">
+        <v>46</v>
+      </c>
+      <c r="L768" s="1">
+        <v>46235</v>
+      </c>
+      <c r="M768" t="s">
+        <v>2385</v>
+      </c>
+      <c r="N768" s="2">
+        <v>46311</v>
+      </c>
+      <c r="O768" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="769" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A769" t="s">
+        <v>15</v>
+      </c>
+      <c r="B769">
+        <v>16763</v>
+      </c>
+      <c r="C769" t="s">
+        <v>16</v>
+      </c>
+      <c r="D769" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E769" t="s">
+        <v>2395</v>
+      </c>
+      <c r="F769" t="s">
+        <v>19</v>
+      </c>
+      <c r="G769" t="s">
+        <v>20</v>
+      </c>
+      <c r="H769" t="s">
+        <v>40</v>
+      </c>
+      <c r="I769" t="s">
+        <v>40</v>
+      </c>
+      <c r="J769" t="s">
+        <v>29</v>
+      </c>
+      <c r="K769" t="s">
+        <v>23</v>
+      </c>
+      <c r="L769" s="1">
+        <v>46235</v>
+      </c>
+      <c r="M769" t="s">
+        <v>2396</v>
+      </c>
+      <c r="N769" s="2">
+        <v>46311</v>
+      </c>
+      <c r="O769" t="s">
         <v>25</v>
       </c>
     </row>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4306C042-AFD0-46B0-9F99-72800189B0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B02551-01BB-48E1-88D0-252A01C473E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9231" uniqueCount="2397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9243" uniqueCount="2400">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7225,6 +7225,15 @@
   </si>
   <si>
     <t>JK15D0178</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJA01822</t>
+  </si>
+  <si>
+    <t>K12NP7918982</t>
+  </si>
+  <si>
+    <t>JK04L5499</t>
   </si>
 </sst>
 </file>
@@ -7599,8 +7608,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O769">
-  <autoFilter ref="A1:O769" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O770">
+  <autoFilter ref="A1:O770" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -7919,7 +7928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O769"/>
+  <dimension ref="A1:O770"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -44078,6 +44087,53 @@
         <v>46311</v>
       </c>
       <c r="O769" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="770" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A770" t="s">
+        <v>15</v>
+      </c>
+      <c r="B770">
+        <v>16763</v>
+      </c>
+      <c r="C770" t="s">
+        <v>16</v>
+      </c>
+      <c r="D770" t="s">
+        <v>2397</v>
+      </c>
+      <c r="E770" t="s">
+        <v>2398</v>
+      </c>
+      <c r="F770" t="s">
+        <v>19</v>
+      </c>
+      <c r="G770" t="s">
+        <v>20</v>
+      </c>
+      <c r="H770" t="s">
+        <v>40</v>
+      </c>
+      <c r="I770" t="s">
+        <v>40</v>
+      </c>
+      <c r="J770" t="s">
+        <v>29</v>
+      </c>
+      <c r="K770" t="s">
+        <v>23</v>
+      </c>
+      <c r="L770" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M770" t="s">
+        <v>2399</v>
+      </c>
+      <c r="N770" s="2">
+        <v>46312</v>
+      </c>
+      <c r="O770" t="s">
         <v>25</v>
       </c>
     </row>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B02551-01BB-48E1-88D0-252A01C473E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDC18EC-6818-4430-BAA5-2AC5D43F253D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9243" uniqueCount="2400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9315" uniqueCount="2421">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7234,6 +7234,69 @@
   </si>
   <si>
     <t>JK04L5499</t>
+  </si>
+  <si>
+    <t>MBJTYKM1STA149901</t>
+  </si>
+  <si>
+    <t>M15DNF29095</t>
+  </si>
+  <si>
+    <t>JK01BG0178</t>
+  </si>
+  <si>
+    <t>MBHHWBC3STJD84645</t>
+  </si>
+  <si>
+    <t>Z12EP4013407</t>
+  </si>
+  <si>
+    <t>JK01BG0265</t>
+  </si>
+  <si>
+    <t>MBJTYKM1STK156437</t>
+  </si>
+  <si>
+    <t>M15DNG85153</t>
+  </si>
+  <si>
+    <t>G VITARA STGHYBRID ALPHA+(O)</t>
+  </si>
+  <si>
+    <t>A WHITE AND M BLACK</t>
+  </si>
+  <si>
+    <t>JK02DX5557</t>
+  </si>
+  <si>
+    <t>MBJTYKL1STK397829</t>
+  </si>
+  <si>
+    <t>K15CN8065255</t>
+  </si>
+  <si>
+    <t>G VITARA SMTHYBRIDZETA(O)AT</t>
+  </si>
+  <si>
+    <t>JK01BG0346</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ984769</t>
+  </si>
+  <si>
+    <t>K12NP7906732</t>
+  </si>
+  <si>
+    <t>JK01BG5007</t>
+  </si>
+  <si>
+    <t>MBHKWD13STG936415</t>
+  </si>
+  <si>
+    <t>K12NP7872879</t>
+  </si>
+  <si>
+    <t>JK01BG0376</t>
   </si>
 </sst>
 </file>
@@ -7608,8 +7671,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O770">
-  <autoFilter ref="A1:O770" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O776">
+  <autoFilter ref="A1:O776" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -7928,7 +7991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O770"/>
+  <dimension ref="A1:O776"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -44134,6 +44197,288 @@
         <v>46312</v>
       </c>
       <c r="O770" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="771" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A771" t="s">
+        <v>15</v>
+      </c>
+      <c r="B771">
+        <v>16763</v>
+      </c>
+      <c r="C771" t="s">
+        <v>16</v>
+      </c>
+      <c r="D771" t="s">
+        <v>2400</v>
+      </c>
+      <c r="E771" t="s">
+        <v>2401</v>
+      </c>
+      <c r="F771" t="s">
+        <v>19</v>
+      </c>
+      <c r="G771" t="s">
+        <v>20</v>
+      </c>
+      <c r="H771" t="s">
+        <v>1291</v>
+      </c>
+      <c r="I771" t="s">
+        <v>1291</v>
+      </c>
+      <c r="J771" t="s">
+        <v>45</v>
+      </c>
+      <c r="K771" t="s">
+        <v>296</v>
+      </c>
+      <c r="L771" s="1">
+        <v>46023</v>
+      </c>
+      <c r="M771" t="s">
+        <v>2402</v>
+      </c>
+      <c r="N771" s="2">
+        <v>46314</v>
+      </c>
+      <c r="O771" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="772" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A772" t="s">
+        <v>15</v>
+      </c>
+      <c r="B772">
+        <v>16763</v>
+      </c>
+      <c r="C772" t="s">
+        <v>16</v>
+      </c>
+      <c r="D772" t="s">
+        <v>2403</v>
+      </c>
+      <c r="E772" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F772" t="s">
+        <v>19</v>
+      </c>
+      <c r="G772" t="s">
+        <v>20</v>
+      </c>
+      <c r="H772" t="s">
+        <v>201</v>
+      </c>
+      <c r="I772" t="s">
+        <v>201</v>
+      </c>
+      <c r="J772" t="s">
+        <v>54</v>
+      </c>
+      <c r="K772" t="s">
+        <v>23</v>
+      </c>
+      <c r="L772" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M772" t="s">
+        <v>2405</v>
+      </c>
+      <c r="N772" s="2">
+        <v>46314</v>
+      </c>
+      <c r="O772" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="773" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A773" t="s">
+        <v>15</v>
+      </c>
+      <c r="B773">
+        <v>16763</v>
+      </c>
+      <c r="C773" t="s">
+        <v>16</v>
+      </c>
+      <c r="D773" t="s">
+        <v>2406</v>
+      </c>
+      <c r="E773" t="s">
+        <v>2407</v>
+      </c>
+      <c r="F773" t="s">
+        <v>19</v>
+      </c>
+      <c r="G773" t="s">
+        <v>20</v>
+      </c>
+      <c r="H773" t="s">
+        <v>2408</v>
+      </c>
+      <c r="I773" t="s">
+        <v>2408</v>
+      </c>
+      <c r="J773" t="s">
+        <v>2409</v>
+      </c>
+      <c r="K773" t="s">
+        <v>296</v>
+      </c>
+      <c r="L773" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M773" t="s">
+        <v>2410</v>
+      </c>
+      <c r="N773" s="2">
+        <v>46314</v>
+      </c>
+      <c r="O773" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="774" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A774" t="s">
+        <v>15</v>
+      </c>
+      <c r="B774">
+        <v>16763</v>
+      </c>
+      <c r="C774" t="s">
+        <v>16</v>
+      </c>
+      <c r="D774" t="s">
+        <v>2411</v>
+      </c>
+      <c r="E774" t="s">
+        <v>2412</v>
+      </c>
+      <c r="F774" t="s">
+        <v>19</v>
+      </c>
+      <c r="G774" t="s">
+        <v>20</v>
+      </c>
+      <c r="H774" t="s">
+        <v>2413</v>
+      </c>
+      <c r="I774" t="s">
+        <v>2413</v>
+      </c>
+      <c r="J774" t="s">
+        <v>115</v>
+      </c>
+      <c r="K774" t="s">
+        <v>46</v>
+      </c>
+      <c r="L774" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M774" t="s">
+        <v>2414</v>
+      </c>
+      <c r="N774" s="2">
+        <v>46316</v>
+      </c>
+      <c r="O774" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="775" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A775" t="s">
+        <v>15</v>
+      </c>
+      <c r="B775">
+        <v>16763</v>
+      </c>
+      <c r="C775" t="s">
+        <v>16</v>
+      </c>
+      <c r="D775" t="s">
+        <v>2415</v>
+      </c>
+      <c r="E775" t="s">
+        <v>2416</v>
+      </c>
+      <c r="F775" t="s">
+        <v>19</v>
+      </c>
+      <c r="G775" t="s">
+        <v>20</v>
+      </c>
+      <c r="H775" t="s">
+        <v>53</v>
+      </c>
+      <c r="I775" t="s">
+        <v>53</v>
+      </c>
+      <c r="J775" t="s">
+        <v>29</v>
+      </c>
+      <c r="K775" t="s">
+        <v>23</v>
+      </c>
+      <c r="L775" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M775" t="s">
+        <v>2417</v>
+      </c>
+      <c r="N775" s="2">
+        <v>46316</v>
+      </c>
+      <c r="O775" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="776" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A776" t="s">
+        <v>15</v>
+      </c>
+      <c r="B776">
+        <v>16763</v>
+      </c>
+      <c r="C776" t="s">
+        <v>16</v>
+      </c>
+      <c r="D776" t="s">
+        <v>2418</v>
+      </c>
+      <c r="E776" t="s">
+        <v>2419</v>
+      </c>
+      <c r="F776" t="s">
+        <v>19</v>
+      </c>
+      <c r="G776" t="s">
+        <v>20</v>
+      </c>
+      <c r="H776" t="s">
+        <v>100</v>
+      </c>
+      <c r="I776" t="s">
+        <v>100</v>
+      </c>
+      <c r="J776" t="s">
+        <v>29</v>
+      </c>
+      <c r="K776" t="s">
+        <v>23</v>
+      </c>
+      <c r="L776" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M776" t="s">
+        <v>2420</v>
+      </c>
+      <c r="N776" s="2">
+        <v>46316</v>
+      </c>
+      <c r="O776" t="s">
         <v>25</v>
       </c>
     </row>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDC18EC-6818-4430-BAA5-2AC5D43F253D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4D0571-086D-40EB-96FC-B88E448EB87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9315" uniqueCount="2421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9327" uniqueCount="2424">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7297,6 +7297,15 @@
   </si>
   <si>
     <t>JK01BG0376</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ986833</t>
+  </si>
+  <si>
+    <t>K12NP7908386</t>
+  </si>
+  <si>
+    <t>LA017663</t>
   </si>
 </sst>
 </file>
@@ -7671,8 +7680,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O776">
-  <autoFilter ref="A1:O776" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O777">
+  <autoFilter ref="A1:O777" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -7991,7 +8000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O776"/>
+  <dimension ref="A1:O777"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -44479,6 +44488,53 @@
         <v>46316</v>
       </c>
       <c r="O776" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="777" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A777" t="s">
+        <v>15</v>
+      </c>
+      <c r="B777">
+        <v>16763</v>
+      </c>
+      <c r="C777" t="s">
+        <v>16</v>
+      </c>
+      <c r="D777" t="s">
+        <v>2421</v>
+      </c>
+      <c r="E777" t="s">
+        <v>2422</v>
+      </c>
+      <c r="F777" t="s">
+        <v>19</v>
+      </c>
+      <c r="G777" t="s">
+        <v>20</v>
+      </c>
+      <c r="H777" t="s">
+        <v>40</v>
+      </c>
+      <c r="I777" t="s">
+        <v>40</v>
+      </c>
+      <c r="J777" t="s">
+        <v>29</v>
+      </c>
+      <c r="K777" t="s">
+        <v>23</v>
+      </c>
+      <c r="L777" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M777" t="s">
+        <v>2423</v>
+      </c>
+      <c r="N777" s="2">
+        <v>46314</v>
+      </c>
+      <c r="O777" t="s">
         <v>25</v>
       </c>
     </row>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4D0571-086D-40EB-96FC-B88E448EB87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C41D21-6C53-4A8A-AB9F-78E74A75FA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9327" uniqueCount="2424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9387" uniqueCount="2439">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7306,6 +7306,51 @@
   </si>
   <si>
     <t>LA017663</t>
+  </si>
+  <si>
+    <t>MBHKWD13STKA11814</t>
+  </si>
+  <si>
+    <t>K12NP7924887</t>
+  </si>
+  <si>
+    <t>JK13L1503</t>
+  </si>
+  <si>
+    <t>MBHKWD13STH969509</t>
+  </si>
+  <si>
+    <t>K12NP7895749</t>
+  </si>
+  <si>
+    <t>JK01BG0544</t>
+  </si>
+  <si>
+    <t>MBHKWD13STKA13368</t>
+  </si>
+  <si>
+    <t>K12NP7925717</t>
+  </si>
+  <si>
+    <t>JK13L1527</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJA01743</t>
+  </si>
+  <si>
+    <t>K12NP7919024</t>
+  </si>
+  <si>
+    <t>JK12E3240</t>
+  </si>
+  <si>
+    <t>MBJTYKL1STK398155</t>
+  </si>
+  <si>
+    <t>K15CN8060334</t>
+  </si>
+  <si>
+    <t>JK01BG1008</t>
   </si>
 </sst>
 </file>
@@ -7680,8 +7725,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O777">
-  <autoFilter ref="A1:O777" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O782">
+  <autoFilter ref="A1:O782" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -8000,7 +8045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O777"/>
+  <dimension ref="A1:O782"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -44535,6 +44580,241 @@
         <v>46314</v>
       </c>
       <c r="O777" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="778" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A778" t="s">
+        <v>15</v>
+      </c>
+      <c r="B778">
+        <v>16763</v>
+      </c>
+      <c r="C778" t="s">
+        <v>16</v>
+      </c>
+      <c r="D778" t="s">
+        <v>2424</v>
+      </c>
+      <c r="E778" t="s">
+        <v>2425</v>
+      </c>
+      <c r="F778" t="s">
+        <v>19</v>
+      </c>
+      <c r="G778" t="s">
+        <v>20</v>
+      </c>
+      <c r="H778" t="s">
+        <v>53</v>
+      </c>
+      <c r="I778" t="s">
+        <v>53</v>
+      </c>
+      <c r="J778" t="s">
+        <v>54</v>
+      </c>
+      <c r="K778" t="s">
+        <v>23</v>
+      </c>
+      <c r="L778" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M778" t="s">
+        <v>2426</v>
+      </c>
+      <c r="N778" s="2">
+        <v>46318</v>
+      </c>
+      <c r="O778" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="779" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A779" t="s">
+        <v>15</v>
+      </c>
+      <c r="B779">
+        <v>16763</v>
+      </c>
+      <c r="C779" t="s">
+        <v>16</v>
+      </c>
+      <c r="D779" t="s">
+        <v>2427</v>
+      </c>
+      <c r="E779" t="s">
+        <v>2428</v>
+      </c>
+      <c r="F779" t="s">
+        <v>19</v>
+      </c>
+      <c r="G779" t="s">
+        <v>20</v>
+      </c>
+      <c r="H779" t="s">
+        <v>53</v>
+      </c>
+      <c r="I779" t="s">
+        <v>53</v>
+      </c>
+      <c r="J779" t="s">
+        <v>74</v>
+      </c>
+      <c r="K779" t="s">
+        <v>23</v>
+      </c>
+      <c r="L779" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M779" t="s">
+        <v>2429</v>
+      </c>
+      <c r="N779" s="2">
+        <v>46318</v>
+      </c>
+      <c r="O779" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="780" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A780" t="s">
+        <v>15</v>
+      </c>
+      <c r="B780">
+        <v>16763</v>
+      </c>
+      <c r="C780" t="s">
+        <v>16</v>
+      </c>
+      <c r="D780" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E780" t="s">
+        <v>2431</v>
+      </c>
+      <c r="F780" t="s">
+        <v>19</v>
+      </c>
+      <c r="G780" t="s">
+        <v>20</v>
+      </c>
+      <c r="H780" t="s">
+        <v>40</v>
+      </c>
+      <c r="I780" t="s">
+        <v>40</v>
+      </c>
+      <c r="J780" t="s">
+        <v>115</v>
+      </c>
+      <c r="K780" t="s">
+        <v>23</v>
+      </c>
+      <c r="L780" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M780" t="s">
+        <v>2432</v>
+      </c>
+      <c r="N780" s="2">
+        <v>46318</v>
+      </c>
+      <c r="O780" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="781" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A781" t="s">
+        <v>15</v>
+      </c>
+      <c r="B781">
+        <v>16763</v>
+      </c>
+      <c r="C781" t="s">
+        <v>16</v>
+      </c>
+      <c r="D781" t="s">
+        <v>2433</v>
+      </c>
+      <c r="E781" t="s">
+        <v>2434</v>
+      </c>
+      <c r="F781" t="s">
+        <v>19</v>
+      </c>
+      <c r="G781" t="s">
+        <v>20</v>
+      </c>
+      <c r="H781" t="s">
+        <v>40</v>
+      </c>
+      <c r="I781" t="s">
+        <v>40</v>
+      </c>
+      <c r="J781" t="s">
+        <v>29</v>
+      </c>
+      <c r="K781" t="s">
+        <v>23</v>
+      </c>
+      <c r="L781" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M781" t="s">
+        <v>2435</v>
+      </c>
+      <c r="N781" s="2">
+        <v>46318</v>
+      </c>
+      <c r="O781" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="782" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A782" t="s">
+        <v>15</v>
+      </c>
+      <c r="B782">
+        <v>16763</v>
+      </c>
+      <c r="C782" t="s">
+        <v>16</v>
+      </c>
+      <c r="D782" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E782" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F782" t="s">
+        <v>19</v>
+      </c>
+      <c r="G782" t="s">
+        <v>20</v>
+      </c>
+      <c r="H782" t="s">
+        <v>111</v>
+      </c>
+      <c r="I782" t="s">
+        <v>111</v>
+      </c>
+      <c r="J782" t="s">
+        <v>45</v>
+      </c>
+      <c r="K782" t="s">
+        <v>1236</v>
+      </c>
+      <c r="L782" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M782" t="s">
+        <v>2438</v>
+      </c>
+      <c r="N782" s="2">
+        <v>46318</v>
+      </c>
+      <c r="O782" t="s">
         <v>25</v>
       </c>
     </row>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C41D21-6C53-4A8A-AB9F-78E74A75FA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F6848E-80B0-4542-8656-5499A7B90AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9387" uniqueCount="2439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9411" uniqueCount="2446">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7351,6 +7351,27 @@
   </si>
   <si>
     <t>JK01BG1008</t>
+  </si>
+  <si>
+    <t>MBHKWD13STKA22622</t>
+  </si>
+  <si>
+    <t>K12NP5010966</t>
+  </si>
+  <si>
+    <t>JK22D8192</t>
+  </si>
+  <si>
+    <t>MBHPA2ASKTH164368</t>
+  </si>
+  <si>
+    <t>1CG3YG403804</t>
+  </si>
+  <si>
+    <t>Pure EV</t>
+  </si>
+  <si>
+    <t>JK01BG0623</t>
   </si>
 </sst>
 </file>
@@ -7725,8 +7746,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O782">
-  <autoFilter ref="A1:O782" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O784">
+  <autoFilter ref="A1:O784" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -8045,7 +8066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O782"/>
+  <dimension ref="A1:O784"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -44815,6 +44836,100 @@
         <v>46318</v>
       </c>
       <c r="O782" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="783" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A783" t="s">
+        <v>15</v>
+      </c>
+      <c r="B783">
+        <v>16763</v>
+      </c>
+      <c r="C783" t="s">
+        <v>16</v>
+      </c>
+      <c r="D783" t="s">
+        <v>2439</v>
+      </c>
+      <c r="E783" t="s">
+        <v>2440</v>
+      </c>
+      <c r="F783" t="s">
+        <v>19</v>
+      </c>
+      <c r="G783" t="s">
+        <v>20</v>
+      </c>
+      <c r="H783" t="s">
+        <v>53</v>
+      </c>
+      <c r="I783" t="s">
+        <v>53</v>
+      </c>
+      <c r="J783" t="s">
+        <v>54</v>
+      </c>
+      <c r="K783" t="s">
+        <v>23</v>
+      </c>
+      <c r="L783" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M783" t="s">
+        <v>2441</v>
+      </c>
+      <c r="N783" s="2">
+        <v>46319</v>
+      </c>
+      <c r="O783" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="784" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A784" t="s">
+        <v>15</v>
+      </c>
+      <c r="B784">
+        <v>16763</v>
+      </c>
+      <c r="C784" t="s">
+        <v>16</v>
+      </c>
+      <c r="D784" t="s">
+        <v>2442</v>
+      </c>
+      <c r="E784" t="s">
+        <v>2443</v>
+      </c>
+      <c r="F784" t="s">
+        <v>19</v>
+      </c>
+      <c r="G784" t="s">
+        <v>20</v>
+      </c>
+      <c r="H784" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I784" t="s">
+        <v>1301</v>
+      </c>
+      <c r="J784" t="s">
+        <v>29</v>
+      </c>
+      <c r="K784" t="s">
+        <v>2444</v>
+      </c>
+      <c r="L784" s="1">
+        <v>46235</v>
+      </c>
+      <c r="M784" t="s">
+        <v>2445</v>
+      </c>
+      <c r="N784" s="2">
+        <v>46319</v>
+      </c>
+      <c r="O784" t="s">
         <v>25</v>
       </c>
     </row>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F6848E-80B0-4542-8656-5499A7B90AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58536131-19D2-487D-B236-891458368DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9411" uniqueCount="2446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9435" uniqueCount="2452">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7372,6 +7372,24 @@
   </si>
   <si>
     <t>JK01BG0623</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJA01834</t>
+  </si>
+  <si>
+    <t>K12NP7919031</t>
+  </si>
+  <si>
+    <t>JK16D1971</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ985277</t>
+  </si>
+  <si>
+    <t>K12NP7907192</t>
+  </si>
+  <si>
+    <t>JK05R2754</t>
   </si>
 </sst>
 </file>
@@ -7746,8 +7764,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O784">
-  <autoFilter ref="A1:O784" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O786">
+  <autoFilter ref="A1:O786" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -8066,7 +8084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O784"/>
+  <dimension ref="A1:O786"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -44930,6 +44948,100 @@
         <v>46319</v>
       </c>
       <c r="O784" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="785" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A785" t="s">
+        <v>15</v>
+      </c>
+      <c r="B785">
+        <v>16763</v>
+      </c>
+      <c r="C785" t="s">
+        <v>16</v>
+      </c>
+      <c r="D785" t="s">
+        <v>2446</v>
+      </c>
+      <c r="E785" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F785" t="s">
+        <v>19</v>
+      </c>
+      <c r="G785" t="s">
+        <v>20</v>
+      </c>
+      <c r="H785" t="s">
+        <v>40</v>
+      </c>
+      <c r="I785" t="s">
+        <v>40</v>
+      </c>
+      <c r="J785" t="s">
+        <v>29</v>
+      </c>
+      <c r="K785" t="s">
+        <v>23</v>
+      </c>
+      <c r="L785" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M785" t="s">
+        <v>2448</v>
+      </c>
+      <c r="N785" s="2">
+        <v>46321</v>
+      </c>
+      <c r="O785" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="786" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A786" t="s">
+        <v>15</v>
+      </c>
+      <c r="B786">
+        <v>16763</v>
+      </c>
+      <c r="C786" t="s">
+        <v>16</v>
+      </c>
+      <c r="D786" t="s">
+        <v>2449</v>
+      </c>
+      <c r="E786" t="s">
+        <v>2450</v>
+      </c>
+      <c r="F786" t="s">
+        <v>19</v>
+      </c>
+      <c r="G786" t="s">
+        <v>20</v>
+      </c>
+      <c r="H786" t="s">
+        <v>53</v>
+      </c>
+      <c r="I786" t="s">
+        <v>53</v>
+      </c>
+      <c r="J786" t="s">
+        <v>54</v>
+      </c>
+      <c r="K786" t="s">
+        <v>23</v>
+      </c>
+      <c r="L786" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M786" t="s">
+        <v>2451</v>
+      </c>
+      <c r="N786" s="2">
+        <v>46321</v>
+      </c>
+      <c r="O786" t="s">
         <v>25</v>
       </c>
     </row>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58536131-19D2-487D-B236-891458368DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F12885-BEF3-40F5-9B15-8BD36640C9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9435" uniqueCount="2452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9483" uniqueCount="2464">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7390,6 +7390,42 @@
   </si>
   <si>
     <t>JK05R2754</t>
+  </si>
+  <si>
+    <t>JK13L1593</t>
+  </si>
+  <si>
+    <t>K12NP7929822</t>
+  </si>
+  <si>
+    <t>MBHKWD13STKA21001</t>
+  </si>
+  <si>
+    <t>JK04L5603</t>
+  </si>
+  <si>
+    <t>K12NP7915641</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ996901</t>
+  </si>
+  <si>
+    <t>JK03R9933</t>
+  </si>
+  <si>
+    <t>K12NP7908293</t>
+  </si>
+  <si>
+    <t>MBHKWD13STJ986743</t>
+  </si>
+  <si>
+    <t>JK13L1540</t>
+  </si>
+  <si>
+    <t>K12NP7927295</t>
+  </si>
+  <si>
+    <t>MBHKWD13STKA16292</t>
   </si>
 </sst>
 </file>
@@ -7764,8 +7800,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O786">
-  <autoFilter ref="A1:O786" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O790">
+  <autoFilter ref="A1:O790" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -8084,7 +8120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O786"/>
+  <dimension ref="A1:O790"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -45042,6 +45078,194 @@
         <v>46321</v>
       </c>
       <c r="O786" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="787" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A787" t="s">
+        <v>15</v>
+      </c>
+      <c r="B787">
+        <v>16763</v>
+      </c>
+      <c r="C787" t="s">
+        <v>16</v>
+      </c>
+      <c r="D787" t="s">
+        <v>2463</v>
+      </c>
+      <c r="E787" t="s">
+        <v>2462</v>
+      </c>
+      <c r="F787" t="s">
+        <v>19</v>
+      </c>
+      <c r="G787" t="s">
+        <v>20</v>
+      </c>
+      <c r="H787" t="s">
+        <v>40</v>
+      </c>
+      <c r="I787" t="s">
+        <v>40</v>
+      </c>
+      <c r="J787" t="s">
+        <v>115</v>
+      </c>
+      <c r="K787" t="s">
+        <v>23</v>
+      </c>
+      <c r="L787" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M787" t="s">
+        <v>2461</v>
+      </c>
+      <c r="N787" s="2">
+        <v>46323</v>
+      </c>
+      <c r="O787" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="788" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A788" t="s">
+        <v>15</v>
+      </c>
+      <c r="B788">
+        <v>16763</v>
+      </c>
+      <c r="C788" t="s">
+        <v>16</v>
+      </c>
+      <c r="D788" t="s">
+        <v>2460</v>
+      </c>
+      <c r="E788" t="s">
+        <v>2459</v>
+      </c>
+      <c r="F788" t="s">
+        <v>19</v>
+      </c>
+      <c r="G788" t="s">
+        <v>20</v>
+      </c>
+      <c r="H788" t="s">
+        <v>53</v>
+      </c>
+      <c r="I788" t="s">
+        <v>53</v>
+      </c>
+      <c r="J788" t="s">
+        <v>29</v>
+      </c>
+      <c r="K788" t="s">
+        <v>23</v>
+      </c>
+      <c r="L788" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M788" t="s">
+        <v>2458</v>
+      </c>
+      <c r="N788" s="2">
+        <v>46323</v>
+      </c>
+      <c r="O788" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="789" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A789" t="s">
+        <v>15</v>
+      </c>
+      <c r="B789">
+        <v>16763</v>
+      </c>
+      <c r="C789" t="s">
+        <v>16</v>
+      </c>
+      <c r="D789" t="s">
+        <v>2457</v>
+      </c>
+      <c r="E789" t="s">
+        <v>2456</v>
+      </c>
+      <c r="F789" t="s">
+        <v>19</v>
+      </c>
+      <c r="G789" t="s">
+        <v>20</v>
+      </c>
+      <c r="H789" t="s">
+        <v>53</v>
+      </c>
+      <c r="I789" t="s">
+        <v>53</v>
+      </c>
+      <c r="J789" t="s">
+        <v>29</v>
+      </c>
+      <c r="K789" t="s">
+        <v>23</v>
+      </c>
+      <c r="L789" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M789" t="s">
+        <v>2455</v>
+      </c>
+      <c r="N789" s="2">
+        <v>46323</v>
+      </c>
+      <c r="O789" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="790" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A790" t="s">
+        <v>15</v>
+      </c>
+      <c r="B790">
+        <v>16763</v>
+      </c>
+      <c r="C790" t="s">
+        <v>16</v>
+      </c>
+      <c r="D790" t="s">
+        <v>2454</v>
+      </c>
+      <c r="E790" t="s">
+        <v>2453</v>
+      </c>
+      <c r="F790" t="s">
+        <v>19</v>
+      </c>
+      <c r="G790" t="s">
+        <v>20</v>
+      </c>
+      <c r="H790" t="s">
+        <v>279</v>
+      </c>
+      <c r="I790" t="s">
+        <v>279</v>
+      </c>
+      <c r="J790" t="s">
+        <v>29</v>
+      </c>
+      <c r="K790" t="s">
+        <v>23</v>
+      </c>
+      <c r="L790" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M790" t="s">
+        <v>2452</v>
+      </c>
+      <c r="N790" s="2">
+        <v>46323</v>
+      </c>
+      <c r="O790" t="s">
         <v>25</v>
       </c>
     </row>

--- a/HSRP.xlsx
+++ b/HSRP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F12885-BEF3-40F5-9B15-8BD36640C9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EECB67-EEDB-4E5D-AC2D-EB2AFFF4A13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{712539EB-9E89-4BB1-9D89-D213A58D3257}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9483" uniqueCount="2464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9495" uniqueCount="2467">
   <si>
     <t>PARENT GROUP</t>
   </si>
@@ -7426,6 +7426,15 @@
   </si>
   <si>
     <t>MBHKWD13STKA16292</t>
+  </si>
+  <si>
+    <t>MBJTYKL1STJ393563</t>
+  </si>
+  <si>
+    <t>K15CN8052863</t>
+  </si>
+  <si>
+    <t>JK22D8227</t>
   </si>
 </sst>
 </file>
@@ -7800,8 +7809,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O790">
-  <autoFilter ref="A1:O790" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}" name="Table1" displayName="Table1" ref="A1:O792">
+  <autoFilter ref="A1:O792" xr:uid="{69F6F882-CDDC-4EC4-8171-B97F848CD4DF}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9CF4C76A-05D0-4E6D-A0D8-0663E989C2E2}" name="PARENT GROUP" totalsRowLabel="Total" totalsRowDxfId="19"/>
     <tableColumn id="2" xr3:uid="{D7189BE0-F1A5-45A1-BF68-955CD0A7FB7F}" name="DEALER MAP CODE"/>
@@ -8120,7 +8129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37263B2-E553-4363-B4F4-E95CFF387734}">
-  <dimension ref="A1:O790"/>
+  <dimension ref="A1:O791"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -45266,6 +45275,53 @@
         <v>46323</v>
       </c>
       <c r="O790" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="791" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A791" t="s">
+        <v>15</v>
+      </c>
+      <c r="B791">
+        <v>16763</v>
+      </c>
+      <c r="C791" t="s">
+        <v>16</v>
+      </c>
+      <c r="D791" t="s">
+        <v>2464</v>
+      </c>
+      <c r="E791" t="s">
+        <v>2465</v>
+      </c>
+      <c r="F791" t="s">
+        <v>19</v>
+      </c>
+      <c r="G791" t="s">
+        <v>20</v>
+      </c>
+      <c r="H791" t="s">
+        <v>300</v>
+      </c>
+      <c r="I791" t="s">
+        <v>300</v>
+      </c>
+      <c r="J791" t="s">
+        <v>45</v>
+      </c>
+      <c r="K791" t="s">
+        <v>1236</v>
+      </c>
+      <c r="L791" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M791" t="s">
+        <v>2466</v>
+      </c>
+      <c r="N791" s="2">
+        <v>46325</v>
+      </c>
+      <c r="O791" t="s">
         <v>25</v>
       </c>
     </row>
